--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55</v>
+        <v>661</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,17 +486,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69/26</t>
+          <t>st. 110</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Říčany-Radošovice</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>č. 69/26 Říčany-Radošovice</t>
+          <t>stavební č. 110 Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -510,11 +510,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56</v>
+        <v>662</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -524,17 +524,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>st. 736</t>
+          <t>172/40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Říčany-Radošovice</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stavební č. 736 Říčany-Radošovice (součástí je stavba č.p. 366, čst obce Radošovice)</t>
+          <t>č. 172/40 Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57</v>
+        <v>663</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -562,17 +562,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>92/13</t>
+          <t>st. 602</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Říčany-Radošovice</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>č. 92/13 Říčany-Radošovice</t>
+          <t>stavební č. 602 Nová Ves u Prahy (součástí je stavba č.p. 519, čst obce Nová Ves)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -580,13 +580,13 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58</v>
+        <v>664</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -600,17 +600,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>561/6</t>
+          <t>173/122</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Říčany-Radošovice</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>č. 561/6 Říčany-Radošovice</t>
+          <t>č. 173/122 Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -624,7 +624,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63</v>
+        <v>665</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -638,17 +638,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>263/2</t>
+          <t>173/127</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Těptín</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>č. 263/2 Těptín</t>
+          <t>č. 173/127 Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -662,11 +662,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64</v>
+        <v>16796</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -676,17 +676,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>516/3</t>
+          <t>st. 323</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Těptín</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>č. 516/3 Těptín</t>
+          <t>stavební č. 323 Nová Ves u Prahy (součástí je stavba č.p. 247, čst obce Nová Ves)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -694,17 +694,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>65</v>
+        <v>16797</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>st. 1105</t>
+          <t>95/66</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Těptín</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>jednotka č. 280014, byt v budově č.p. 28, část obce Kamenice, na parcele st. 1105 Těptín, podíl na společných částech domu a pozemku 381/6380</t>
+          <t>č. 95/66 Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -732,17 +732,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66</v>
+        <v>16798</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>619/1</t>
+          <t>st. 298</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Těptín</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>č. 619/1 Těptín</t>
+          <t>jednotka č. 2650083, byt v budově č.p. 265, část obce Nová Ves, na parcele st. 298 Nová Ves u Prahy, podíl na společných částech domu a pozemku 620/1984</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -770,13 +770,13 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele s prefixem st. + KU</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67</v>
+        <v>16799</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -790,17 +790,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>725/28</t>
+          <t>95/218</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Těptín</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 725/28 Těptín</t>
+          <t>č. 95/218 Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -814,11 +814,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68</v>
+        <v>16800</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>st. 1603</t>
+          <t>95/131</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Těptín</t>
+          <t>Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stavební č. 1603 Těptín (součástí je stavba č.p. 2833, čst obce Těptín)</t>
+          <t>č. 95/131 Nová Ves u Prahy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>

--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>661</v>
+        <v>58842</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -481,22 +481,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>st. 110</t>
+          <t>1044/2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stavební č. 110 Nová Ves u Prahy</t>
+          <t>č. 1044/2 Libuš</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -510,31 +510,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>662</v>
+        <v>58841</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>172/40</t>
+          <t>1044/4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>č. 172/40 Nová Ves u Prahy</t>
+          <t>č. 1044/4 Libuš (součástí je stavba č.p. 957, čst obce Libuš)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,37 +542,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>663</v>
+        <v>58840</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>st. 602</t>
+          <t>1087/2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stavební č. 602 Nová Ves u Prahy (součástí je stavba č.p. 519, čst obce Nová Ves)</t>
+          <t>č. 1087/2 Libuš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -580,13 +580,13 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>664</v>
+        <v>58839</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -595,22 +595,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>173/122</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>č. 173/122 Nová Ves u Prahy</t>
+          <t>č. 1088 Libuš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -624,31 +624,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>665</v>
+        <v>58838</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>173/127</t>
+          <t>1087/1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>č. 173/127 Nová Ves u Prahy</t>
+          <t>č. 1087/1 Libuš (součástí je stavba č.p. 435, čst obce Libuš)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -656,37 +656,37 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16796</v>
+        <v>58837</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>st. 323</t>
+          <t>546/1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stavební č. 323 Nová Ves u Prahy (součástí je stavba č.p. 247, čst obce Nová Ves)</t>
+          <t>č. 546/1 Libuš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -694,13 +694,13 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16797</v>
+        <v>58836</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -709,22 +709,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>95/66</t>
+          <t>546/3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>č. 95/66 Nová Ves u Prahy</t>
+          <t>č. 546/3 Libuš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,31 +738,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16798</v>
+        <v>58835</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>st. 298</t>
+          <t>546/2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>jednotka č. 2650083, byt v budově č.p. 265, část obce Nová Ves, na parcele st. 298 Nová Ves u Prahy, podíl na společných částech domu a pozemku 620/1984</t>
+          <t>č. 546/2 Libuš (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -770,37 +770,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16799</v>
+        <v>58834</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>95/218</t>
+          <t>546/4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Libuš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 95/218 Nová Ves u Prahy</t>
+          <t>č. 546/4 Libuš (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -808,13 +808,13 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16800</v>
+        <v>58833</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -823,28 +823,2042 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>95/131</t>
+          <t>835/84</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nová Ves u Prahy</t>
+          <t>Písnice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>č. 95/131 Nová Ves u Prahy</t>
+          <t>č. 835/84 Písnice</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>58832</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>č. 761 Písnice</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>58831</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>č. 760 Písnice (součástí je stavba č.p. 329, čst obce Písnice)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>58830</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>910/2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>58830</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>910/3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>58830</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>910/4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>58830</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>910/5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>58830</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>910/6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>58830</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>910/7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Písnice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>58829</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2197/2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>č. 2197/2 Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>58828</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>st. 500</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stavební č. 500 Ledeč nad Sázavou (součástí je stavba č.p. 117, čst obce Horní Ledeč)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>58827</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>st. 825</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>jednotka č. 6450002, byt v budově č.p. 645, 646, část obce Ledeč nad Sázavou, na parcele st. 825 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 237/12278</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>jednotka na parcele s prefixem st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>58826</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2090/24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>č. 2090/24 Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>58825</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>st. 614</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>jednotka č. 5540005, byt v budově č.p. 553, 554, část obce Ledeč nad Sázavou, na parcele st. 614 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 629/8741</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>jednotka na parcele s prefixem st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>58824</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>st. 722</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>jednotka č. 6700007, byt v budově č.p. 670, část obce Ledeč nad Sázavou, na parcele st. 722 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 52/1000</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>jednotka na parcele s prefixem st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>58823</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>823/5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>č. 823/5 Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>58822</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>823/25</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>č. 823/25 Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>58821</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>823/32</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>č. 823/32 Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>58820</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>st. 1640</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>stavební č. 1640 Ledeč nad Sázavou (součástí je stavba budova bez čp/če, garáž)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>58819</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>st. 710/2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>stavební č. 710/2 Ledeč nad Sázavou (součástí je stavba budova bez čp/če, jiná stavba)</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>58818</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>st. 710/1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>stavební č. 710/1 Ledeč nad Sázavou (součástí je stavba č.p. 674, čst obce Ledeč nad Sázavou)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>58817</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>č. 964 Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>58816</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>st. 601</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>jednotka č. 5560004, byt v budově č.p. 557, 555, 556, část obce Ledeč nad Sázavou, na parcele st. 601 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 519/9693</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>jednotka na parcele s prefixem st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>58815</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>429/48</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>jednotka č. 9860006, garáž v budově č.p. 986, část obce Libuš, na parcele 429/48 Libuš, podíl na společných částech domu a pozemku 184814/679789</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>58814</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>429/48</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>jednotka č. 9860410, byt v budově č.p. 986, část obce Libuš, na parcele 429/48 Libuš, podíl na společných částech domu a pozemku 5732/679789</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>58813</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1123/116</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>č. 1123/116 Libuš</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>58812</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1123/76</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>č. 1123/76 Libuš</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>58811</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1123/73</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>č. 1123/73 Libuš</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>58810</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1123/120</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>č. 1123/120 Libuš</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>58809</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1123/118</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>č. 1123/118 Libuš</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>58808</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1123/119</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>č. 1123/119 Libuš</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>58807</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1123/117</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Libuš</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>č. 1123/117 Libuš</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>58806</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2382/8</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>č. 2382/8 Kunratice</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>58805</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2342/27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>č. 2342/27 Kunratice</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>58804</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2342/30</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>č. 2342/30 Kunratice</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>58803</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2342/28</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>č. 2342/28 Kunratice</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>58802</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2342/29</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>č. 2342/29 Kunratice</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>58801</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2342/31</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>č. 2342/31 Kunratice</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>58800</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2342/27</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>58800</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2342/28</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>58800</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2342/29</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>58800</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2342/30</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>58800</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2342/31</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>58799</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2342/27</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>58799</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2342/28</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>58799</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2342/29</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>58799</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2342/30</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>58799</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2342/31</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58798</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1433/13</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>č. 1433/13 Kunratice</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58797</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1433/12</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>č. 1433/12 Kunratice</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>58796</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>59/12</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>č. 59/12 Kunratice</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>58795</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>59/45</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>č. 59/45 Kunratice (součástí je stavba č.p. 1045, čst obce Kunratice)</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>58794</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>267/9</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>budova bez čp/če, jiná stavba, na parcele 267/9 Kunratice</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>budova na parcele č.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>58793</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2428/21</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>č. 2428/21 Kunratice</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>číslo a KU za ním</t>
         </is>

--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,31 +472,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58842</v>
+        <v>47800</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1044/2</t>
+          <t>st. 646</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>č. 1044/2 Libuš</t>
+          <t>jednotka č. 4680004, byt v budově č.p. 468, 467, 469, část obce Olešovice, na parcele st. 646 Ládví, podíl na společných částech domu a pozemku 7596/110533</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -504,37 +504,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele s prefixem st. + KU</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58841</v>
+        <v>47799</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1044/4</t>
+          <t>748/43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>č. 1044/4 Libuš (součástí je stavba č.p. 957, čst obce Libuš)</t>
+          <t>č. 748/43 Ládví</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,37 +542,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58840</v>
+        <v>47798</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1087/2</t>
+          <t>st. 334</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>č. 1087/2 Libuš</t>
+          <t>stavební č. 334 Ládví (součástí je stavba č.p. 154, čst obce Ládví)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -580,13 +580,13 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58839</v>
+        <v>47797</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -595,22 +595,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>125/12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>č. 1088 Libuš</t>
+          <t>č. 125/12 Ládví</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -624,7 +624,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>58838</v>
+        <v>47796</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -633,22 +633,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1087/1</t>
+          <t>st. 1372</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>č. 1087/1 Libuš (součástí je stavba č.p. 435, čst obce Libuš)</t>
+          <t>stavební č. 1372 Ládví (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -662,31 +662,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58837</v>
+        <v>47795</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>546/1</t>
+          <t>st. 514</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>č. 546/1 Libuš</t>
+          <t>stavební č. 514 Ládví (součástí je stavba č.e. 1347, čst obce Ládví)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -694,13 +694,13 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58836</v>
+        <v>47794</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -709,22 +709,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>546/3</t>
+          <t>255/8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>č. 546/3 Libuš</t>
+          <t>č. 255/8 Ládví</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,31 +738,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58835</v>
+        <v>47793</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>546/2</t>
+          <t>722/12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>č. 546/2 Libuš (součástí je stavba budova bez čp/če, jiná stavba)</t>
+          <t>č. 722/12 Ládví</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -770,37 +770,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>58834</v>
+        <v>47792</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>546/4</t>
+          <t>234/4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 546/4 Libuš (součástí je stavba budova bez čp/če, jiná stavba)</t>
+          <t>č. 234/4 Ládví</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -808,13 +808,13 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58833</v>
+        <v>47791</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -823,22 +823,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>835/84</t>
+          <t>646/32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>č. 835/84 Písnice</t>
+          <t>č. 646/32 Ládví</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -852,31 +852,31 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>58832</v>
+        <v>47790</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>st. 877</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>č. 761 Písnice</t>
+          <t>stavební č. 877 Ládví (součástí je stavba č.p. 1425, čst obce Olešovice)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -884,37 +884,37 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>58831</v>
+        <v>47789</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>628/4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>č. 760 Písnice (součástí je stavba č.p. 329, čst obce Písnice)</t>
+          <t>č. 628/4 Ládví</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -922,37 +922,37 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>58830</v>
+        <v>47788</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>910/2</t>
+          <t>628/33</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+          <t>č. 628/33 Ládví</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -960,13 +960,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>58830</v>
+        <v>47787</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -975,22 +975,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>910/3</t>
+          <t>st. 1313</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+          <t>jednotka č. 24010022, byt v budově č.p. 2401, část obce Olešovice, na parcele st. 1313 Ládví (součástí je stavba č.p. 2401, čst obce Olešovice), podíl na společných částech domu a pozemku 458/4518</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -998,37 +998,37 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>jednotka na parcele s prefixem st. + KU</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>58830</v>
+        <v>47786</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>910/4</t>
+          <t>634/4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+          <t>č. 634/4 Ládví</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1036,37 +1036,37 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>58830</v>
+        <v>47785</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>910/5</t>
+          <t>634/5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+          <t>č. 634/5 Ládví</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1074,37 +1074,37 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>58830</v>
+        <v>47784</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>910/6</t>
+          <t>328/91</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+          <t>č. 328/91 Ládví</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1112,37 +1112,37 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>58830</v>
+        <v>47783</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>910/7</t>
+          <t>328/143</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>jednotka č. 3660007, byt v budově č.p. 361, 362, 363, 364, 365, 366, část obce Písnice, na parcele 910/2 Písnice (*), 910/3 Písnice (*), 910/4 Písnice (*), 910/5 Písnice (*), 910/6 Písnice (*), 910/7 Písnice, podíl na společných částech domu a pozemku 106/10000</t>
+          <t>č. 328/143 Ládví</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1150,13 +1150,13 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>58829</v>
+        <v>47782</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2197/2</t>
+          <t>414/49</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>č. 2197/2 Ledeč nad Sázavou</t>
+          <t>č. 414/49 Ládví</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1194,31 +1194,31 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>58828</v>
+        <v>47781</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>st. 500</t>
+          <t>414/48</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stavební č. 500 Ledeč nad Sázavou (součástí je stavba č.p. 117, čst obce Horní Ledeč)</t>
+          <t>č. 414/48 Ládví</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1226,37 +1226,37 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>58827</v>
+        <v>47780</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>st. 825</t>
+          <t>st. 1294</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>jednotka č. 6450002, byt v budově č.p. 645, 646, část obce Ledeč nad Sázavou, na parcele st. 825 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 237/12278</t>
+          <t>stavební č. 1294 Ládví (součástí je stavba budova bez čp/če, garáž)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1264,13 +1264,13 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>58826</v>
+        <v>47779</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1279,22 +1279,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2090/24</t>
+          <t>95/15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>č. 2090/24 Ledeč nad Sázavou</t>
+          <t>č. 95/15 Ládví</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1308,31 +1308,31 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>58825</v>
+        <v>47778</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>st. 614</t>
+          <t>96/5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>jednotka č. 5540005, byt v budově č.p. 553, 554, část obce Ledeč nad Sázavou, na parcele st. 614 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 629/8741</t>
+          <t>č. 96/5 Ládví</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1340,37 +1340,37 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>58824</v>
+        <v>47777</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>st. 722</t>
+          <t>97/10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>jednotka č. 6700007, byt v budově č.p. 670, část obce Ledeč nad Sázavou, na parcele st. 722 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 52/1000</t>
+          <t>č. 97/10 Ládví</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1378,37 +1378,37 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>58823</v>
+        <v>47776</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>823/5</t>
+          <t>st. 1315</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>č. 823/5 Ledeč nad Sázavou</t>
+          <t>stavební č. 1315 Ládví (součástí je stavba č.p. 2132, čst obce Ládví)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1416,13 +1416,13 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>58822</v>
+        <v>47775</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1431,22 +1431,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>823/25</t>
+          <t>511/4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>č. 823/25 Ledeč nad Sázavou</t>
+          <t>č. 511/4 Ládví</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1460,7 +1460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>58821</v>
+        <v>47774</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>823/32</t>
+          <t>103/17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>č. 823/32 Ledeč nad Sázavou</t>
+          <t>č. 103/17 Ládví</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1498,31 +1498,31 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>58820</v>
+        <v>47773</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>st. 1640</t>
+          <t>27/10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stavební č. 1640 Ledeč nad Sázavou (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 27/10 Ládví</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1530,37 +1530,37 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>58819</v>
+        <v>47772</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>st. 710/2</t>
+          <t>103/16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stavební č. 710/2 Ledeč nad Sázavou (součástí je stavba budova bez čp/če, jiná stavba)</t>
+          <t>č. 103/16 Ládví</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1568,37 +1568,37 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>58818</v>
+        <v>47771</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>st. 710/1</t>
+          <t>103/12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stavební č. 710/1 Ledeč nad Sázavou (součástí je stavba č.p. 674, čst obce Ledeč nad Sázavou)</t>
+          <t>č. 103/12 Ládví</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1606,13 +1606,13 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>58817</v>
+        <v>47770</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1621,22 +1621,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>102/8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>č. 964 Ledeč nad Sázavou</t>
+          <t>č. 102/8 Ládví</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1650,31 +1650,31 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>58816</v>
+        <v>47769</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>st. 601</t>
+          <t>103/10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ledeč nad Sázavou</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>jednotka č. 5560004, byt v budově č.p. 557, 555, 556, část obce Ledeč nad Sázavou, na parcele st. 601 Ledeč nad Sázavou, podíl na společných částech domu a pozemku 519/9693</t>
+          <t>č. 103/10 Ládví</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1682,37 +1682,37 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>58815</v>
+        <v>47768</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>429/48</t>
+          <t>103/13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>jednotka č. 9860006, garáž v budově č.p. 986, část obce Libuš, na parcele 429/48 Libuš, podíl na společných částech domu a pozemku 184814/679789</t>
+          <t>č. 103/13 Ládví</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1720,13 +1720,13 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>58814</v>
+        <v>47767</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>429/48</t>
+          <t>st. 118</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>jednotka č. 9860410, byt v budově č.p. 986, část obce Libuš, na parcele 429/48 Libuš, podíl na společných částech domu a pozemku 5732/679789</t>
+          <t>jednotka č. 11480029, byt v budově č.p. 1148, část obce Ládví, na parcele st. 118 Ládví, podíl na společných částech domu a pozemku 732/32916</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1758,13 +1758,13 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>jednotka na parcele s prefixem st. + KU</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>58813</v>
+        <v>47766</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1773,22 +1773,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1123/116</t>
+          <t>364/36</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>č. 1123/116 Libuš</t>
+          <t>č. 364/36 Ládví</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1802,7 +1802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>58812</v>
+        <v>47765</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1811,22 +1811,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1123/76</t>
+          <t>798</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>č. 1123/76 Libuš</t>
+          <t>č. 798 Ládví</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>58811</v>
+        <v>47764</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1849,22 +1849,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1123/73</t>
+          <t>618/9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>č. 1123/73 Libuš</t>
+          <t>č. 618/9 Ládví</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1878,31 +1878,31 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>58810</v>
+        <v>47763</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1123/120</t>
+          <t>st. 931</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>č. 1123/120 Libuš</t>
+          <t>stavební č. 931 Ládví (součástí je stavba č.p. 1434, čst obce Olešovice)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1910,13 +1910,13 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>58809</v>
+        <v>47762</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1925,22 +1925,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1123/118</t>
+          <t>578/3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>č. 1123/118 Libuš</t>
+          <t>č. 578/3 Ládví</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>58808</v>
+        <v>47761</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1963,22 +1963,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1123/119</t>
+          <t>578/2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>č. 1123/119 Libuš</t>
+          <t>č. 578/2 Ládví</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1992,7 +1992,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>58807</v>
+        <v>47760</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2001,22 +2001,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1123/117</t>
+          <t>578/1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Libuš</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>č. 1123/117 Libuš</t>
+          <t>č. 578/1 Ládví</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>58806</v>
+        <v>47759</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2039,22 +2039,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2382/8</t>
+          <t>340/1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>č. 2382/8 Kunratice</t>
+          <t>č. 340/1 Ládví</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2068,7 +2068,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>58805</v>
+        <v>47758</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2077,22 +2077,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2342/27</t>
+          <t>432/9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>č. 2342/27 Kunratice</t>
+          <t>č. 432/9 Ládví</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2106,7 +2106,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>58804</v>
+        <v>47757</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2115,22 +2115,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2342/30</t>
+          <t>432/8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>č. 2342/30 Kunratice</t>
+          <t>č. 432/8 Ládví</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>58803</v>
+        <v>47756</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2153,22 +2153,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2342/28</t>
+          <t>430/2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>č. 2342/28 Kunratice</t>
+          <t>č. 430/2 Ládví</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>58802</v>
+        <v>47755</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2342/29</t>
+          <t>459/9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>č. 2342/29 Kunratice</t>
+          <t>č. 459/9 Ládví</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>58801</v>
+        <v>47754</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2229,22 +2229,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2342/31</t>
+          <t>st. 1186</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>č. 2342/31 Kunratice</t>
+          <t>stavební č. 1186 Ládví (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2258,31 +2258,31 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>58800</v>
+        <v>47753</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2342/27</t>
+          <t>st. 476</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+          <t>stavební č. 476 Ládví (součástí je stavba č.e. 1424, čst obce Ládví)</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2290,37 +2290,37 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>58800</v>
+        <v>47752</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2342/28</t>
+          <t>519/1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+          <t>č. 519/1 Ládví</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2328,37 +2328,37 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>58800</v>
+        <v>47751</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2342/29</t>
+          <t>st. 128</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
+          <t>stavební č. 128 Ládví (součástí je stavba č.e. 1485, čst obce Ládví)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2366,501 +2366,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>58800</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>jednotka</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2342/30</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>více parcel oddělených čárkou</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>58800</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>jednotka</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2342/31</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>jednotka č. 11500902, garáž v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 17/7754</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>více parcel oddělených čárkou</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>58799</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>jednotka</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2342/27</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>58799</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>jednotka</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2342/28</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>více parcel oddělených čárkou</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>58799</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>jednotka</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2342/29</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>více parcel oddělených čárkou</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>58799</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>jednotka</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2342/30</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>více parcel oddělených čárkou</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>58799</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>jednotka</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2342/31</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>jednotka č. 11500061, byt v budově č.p. 1152, 1148, 1149, 1150, 1151, část obce Kunratice, na parcele 2342/27 Kunratice, 2342/28 Kunratice, 2342/29 Kunratice, 2342/30 Kunratice, 2342/31 Kunratice, podíl na společných částech domu a pozemku 82/7754</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>více parcel oddělených čárkou</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58798</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1433/13</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>č. 1433/13 Kunratice</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>číslo a KU za ním</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>58797</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1433/12</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>č. 1433/12 Kunratice</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>číslo a KU za ním</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>58796</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>59/12</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>č. 59/12 Kunratice</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>číslo a KU za ním</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>58795</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>budova</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>59/45</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>č. 59/45 Kunratice (součástí je stavba č.p. 1045, čst obce Kunratice)</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
           <t>č. + KU</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>58794</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>budova</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>267/9</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>budova bez čp/če, jiná stavba, na parcele 267/9 Kunratice</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>budova na parcele č.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>58793</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2428/21</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>č. 2428/21 Kunratice</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>

--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,31 +472,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39648</v>
+        <v>47800</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>st. 646</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>budova bez čp/če, garáž, na parcele 4410 Dejvice</t>
+          <t>jednotka č. 4680004, byt v budově č.p. 468, 467, 469, část obce Olešovice, na parcele st. 646 Ládví, podíl na společných částech domu a pozemku 7596/110533</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -504,37 +504,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>budova na parcele č.</t>
+          <t>jednotka na parcele s prefixem st. + KU</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>39322</v>
+        <v>47799</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2904/14</t>
+          <t>748/43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>č. 2904/14 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 748/43 Ládví</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,13 +542,13 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>39257</v>
+        <v>47798</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -557,22 +557,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2747/94</t>
+          <t>st. 334</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>č. 2747/94 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>stavební č. 334 Ládví (součástí je stavba č.p. 154, čst obce Ládví)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,31 +586,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>39190</v>
+        <v>47797</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>244/13</t>
+          <t>125/12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>č. 244/13 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 125/12 Ládví</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -618,13 +618,13 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>39189</v>
+        <v>47796</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -633,22 +633,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1123/49</t>
+          <t>st. 1372</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>č. 1123/49 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>stavební č. 1372 Ládví (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -662,7 +662,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38796</v>
+        <v>47795</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -671,22 +671,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2904/16</t>
+          <t>st. 514</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>č. 2904/16 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>stavební č. 514 Ládví (součástí je stavba č.e. 1347, čst obce Ládví)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -700,31 +700,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>38766</v>
+        <v>47794</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>255/8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>budova bez čp/če, garáž, na parcele 4416 Dejvice</t>
+          <t>č. 255/8 Ládví</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -732,37 +732,37 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>budova na parcele č.</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>38744</v>
+        <v>47793</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>729/92</t>
+          <t>722/12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>budova bez čp/če, garáž, na parcele 729/92 Dejvice</t>
+          <t>č. 722/12 Ládví</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -770,37 +770,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>budova na parcele č.</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>38658</v>
+        <v>47792</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2747/96</t>
+          <t>234/4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 2747/96 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 234/4 Ládví</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -808,37 +808,37 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>38621</v>
+        <v>47791</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>244/31</t>
+          <t>646/32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>č. 244/31 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 646/32 Ládví</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -846,13 +846,13 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>38611</v>
+        <v>47790</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -861,22 +861,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>729/100</t>
+          <t>st. 877</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>budova bez čp/če, garáž, na parcele 729/100 Dejvice</t>
+          <t>stavební č. 877 Ládví (součástí je stavba č.p. 1425, čst obce Olešovice)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -884,37 +884,37 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>budova na parcele č.</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>38596</v>
+        <v>47789</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3128/30</t>
+          <t>628/4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>č. 3128/30 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 628/4 Ládví</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -922,37 +922,37 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>38587</v>
+        <v>47788</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3007/13</t>
+          <t>628/33</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>budova bez čp/če, garáž, na parcele 3007/13 Dejvice</t>
+          <t>č. 628/33 Ládví</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -960,37 +960,37 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>budova na parcele č.</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15164</v>
+        <v>47787</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Praha-východ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>st. 1313</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dejvice</t>
+          <t>Ládví</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>budova bez čp/če, garáž, na parcele 4408 Dejvice</t>
+          <t>jednotka č. 24010022, byt v budově č.p. 2401, část obce Olešovice, na parcele st. 1313 Ládví (součástí je stavba č.p. 2401, čst obce Olešovice), podíl na společných částech domu a pozemku 458/4518</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -998,43 +998,1373 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>budova na parcele č.</t>
+          <t>jednotka na parcele s prefixem st. + KU</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12669</v>
+        <v>47786</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>634/4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>č. 634/4 Ládví</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>47785</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>634/5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>č. 634/5 Ládví</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>47784</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>328/91</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>č. 328/91 Ládví</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>47783</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>328/143</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>č. 328/143 Ládví</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>47782</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>414/49</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>č. 414/49 Ládví</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>47781</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>414/48</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>č. 414/48 Ládví</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>47780</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>budova</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>244/39</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Dejvice</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>č. 244/39 Dejvice (součástí je stavba budova bez čp/če, garáž)</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>st. 1294</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>stavební č. 1294 Ládví (součástí je stavba budova bez čp/če, garáž)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>47779</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>95/15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>č. 95/15 Ládví</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>47778</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>96/5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>č. 96/5 Ládví</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>47777</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>97/10</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>č. 97/10 Ládví</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>47776</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>st. 1315</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>stavební č. 1315 Ládví (součástí je stavba č.p. 2132, čst obce Ládví)</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>47775</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>511/4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>č. 511/4 Ládví</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>47774</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>103/17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>č. 103/17 Ládví</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>47773</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>č. 27/10 Ládví</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>47772</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>103/16</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>č. 103/16 Ládví</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>47771</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>103/12</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>č. 103/12 Ládví</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>47770</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>102/8</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>č. 102/8 Ládví</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>47769</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>103/10</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>č. 103/10 Ládví</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>47768</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>103/13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>č. 103/13 Ládví</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>47767</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>st. 118</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>jednotka č. 11480029, byt v budově č.p. 1148, část obce Ládví, na parcele st. 118 Ládví, podíl na společných částech domu a pozemku 732/32916</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>jednotka na parcele s prefixem st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>47766</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>364/36</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>č. 364/36 Ládví</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>47765</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>č. 798 Ládví</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>47764</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>618/9</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>č. 618/9 Ládví</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>47763</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>st. 931</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>stavební č. 931 Ládví (součástí je stavba č.p. 1434, čst obce Olešovice)</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>47762</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>578/3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>č. 578/3 Ládví</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>47761</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>578/2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>č. 578/2 Ládví</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>47760</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>578/1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>č. 578/1 Ládví</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>47759</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>340/1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>č. 340/1 Ládví</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>47758</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>432/9</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>č. 432/9 Ládví</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>47757</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>432/8</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>č. 432/8 Ládví</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>47756</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>430/2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>č. 430/2 Ládví</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>47755</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>459/9</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>č. 459/9 Ládví</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47754</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>st. 1186</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>stavební č. 1186 Ládví (součástí je stavba budova bez čp/če, jiná stavba)</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47753</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>st. 476</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>stavební č. 476 Ládví (součástí je stavba č.e. 1424, čst obce Ládví)</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>47752</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>519/1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>č. 519/1 Ládví</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>47751</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Praha-východ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>st. 128</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ládví</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>stavební č. 128 Ládví (součástí je stavba č.e. 1485, čst obce Ládví)</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>č. + KU</t>
         </is>

--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>47800</v>
+        <v>55243</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -481,22 +481,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>st. 646</t>
+          <t>1921/32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jednotka č. 4680004, byt v budově č.p. 468, 467, 469, část obce Olešovice, na parcele st. 646 Ládví, podíl na společných částech domu a pozemku 7596/110533</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -504,37 +504,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>47799</v>
+        <v>55243</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>748/43</t>
+          <t>1921/33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>č. 748/43 Ládví</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,37 +542,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47798</v>
+        <v>55243</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>st. 334</t>
+          <t>1921/34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stavební č. 334 Ládví (součástí je stavba č.p. 154, čst obce Ládví)</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -580,37 +580,37 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>47797</v>
+        <v>55243</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>125/12</t>
+          <t>1921/35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>č. 125/12 Ládví</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -618,37 +618,37 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47796</v>
+        <v>55243</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>st. 1372</t>
+          <t>1921/36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stavební č. 1372 Ládví (součástí je stavba budova bez čp/če, jiná stavba)</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -656,37 +656,37 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>47795</v>
+        <v>55243</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>st. 514</t>
+          <t>1921/37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stavební č. 514 Ládví (součástí je stavba č.e. 1347, čst obce Ládví)</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -694,37 +694,37 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47794</v>
+        <v>55243</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>255/8</t>
+          <t>1921/38</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>č. 255/8 Ládví</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -732,37 +732,37 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47793</v>
+        <v>55243</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>722/12</t>
+          <t>1921/39</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Braník</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>č. 722/12 Ládví</t>
+          <t>jednotka č. 508, garáž v budově budova bez čp/če, garáž, na parcele 1921/32 Braník, 1921/33 Braník, 1921/34 Braník, 1921/35 Braník, 1921/36 Braník, 1921/37 Braník, 1921/38 Braník, 1921/39 Braník, podíl na společných částech domu a pozemku 19/140</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -770,37 +770,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47792</v>
+        <v>52108</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>234/4</t>
+          <t>1857/142</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Kamýk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 234/4 Ládví</t>
+          <t>jednotka č. 4640062, garáž v budově č.p. 464, část obce Kamýk, na parcele 1857/142 Kamýk, podíl na společných částech domu a pozemku 291/62868</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -808,37 +808,37 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47791</v>
+        <v>51882</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>646/32</t>
+          <t>1765/5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Nusle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>č. 646/32 Ládví</t>
+          <t>jednotka č. 17410902, garáž v budově č.p. 1741, část obce Nusle, na parcele 1765/5 Nusle (součástí je stavba č.p. 1741, čst obce Nusle), podíl na společných částech domu a pozemku 23569/70347</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -846,37 +846,37 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47790</v>
+        <v>51450</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>st. 877</t>
+          <t>1857/142</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Kamýk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stavební č. 877 Ládví (součástí je stavba č.p. 1425, čst obce Olešovice)</t>
+          <t>jednotka č. 4640105, garáž v budově č.p. 464, část obce Kamýk, na parcele 1857/142 Kamýk, podíl na společných částech domu a pozemku 276/62868</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -884,37 +884,37 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47789</v>
+        <v>49904</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>628/4</t>
+          <t>2114/3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>č. 628/4 Ládví</t>
+          <t>jednotka č. 15680103, garáž v budově č.p. 1570, 1568, 1569, část obce Krč, na parcele 2114/3 Krč, 2114/4 Krč, 2114/5 Krč, podíl na společných částech domu a pozemku 2230/184350</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -922,37 +922,37 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>47788</v>
+        <v>49904</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>628/33</t>
+          <t>2114/4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>č. 628/33 Ládví</t>
+          <t>jednotka č. 15680103, garáž v budově č.p. 1570, 1568, 1569, část obce Krč, na parcele 2114/3 Krč, 2114/4 Krč, 2114/5 Krč, podíl na společných částech domu a pozemku 2230/184350</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -960,13 +960,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47787</v>
+        <v>49904</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -975,22 +975,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>st. 1313</t>
+          <t>2114/5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>jednotka č. 24010022, byt v budově č.p. 2401, část obce Olešovice, na parcele st. 1313 Ládví (součástí je stavba č.p. 2401, čst obce Olešovice), podíl na společných částech domu a pozemku 458/4518</t>
+          <t>jednotka č. 15680103, garáž v budově č.p. 1570, 1568, 1569, část obce Krč, na parcele 2114/3 Krč, 2114/4 Krč, 2114/5 Krč, podíl na společných částech domu a pozemku 2230/184350</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -998,37 +998,37 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>47786</v>
+        <v>39291</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>634/4</t>
+          <t>2715/2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Dejvice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>č. 634/4 Ládví</t>
+          <t>jednotka č. 28220301, garáž v budově č.p. 2822, část obce Dejvice, na parcele 2715/2 Dejvice (součástí je stavba č.p. 2822, čst obce Dejvice), 2715/96 Dejvice, 2715/97 Dejvice, podíl na společných částech domu a pozemku 21306/116531</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1036,37 +1036,37 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47785</v>
+        <v>39291</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>634/5</t>
+          <t>2715/96</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Dejvice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>č. 634/5 Ládví</t>
+          <t>jednotka č. 28220301, garáž v budově č.p. 2822, část obce Dejvice, na parcele 2715/2 Dejvice (součástí je stavba č.p. 2822, čst obce Dejvice), 2715/96 Dejvice, 2715/97 Dejvice, podíl na společných částech domu a pozemku 21306/116531</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1074,37 +1074,37 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47784</v>
+        <v>39291</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>328/91</t>
+          <t>2715/97</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Dejvice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>č. 328/91 Ládví</t>
+          <t>jednotka č. 28220301, garáž v budově č.p. 2822, část obce Dejvice, na parcele 2715/2 Dejvice (součástí je stavba č.p. 2822, čst obce Dejvice), 2715/96 Dejvice, 2715/97 Dejvice, podíl na společných částech domu a pozemku 21306/116531</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1112,37 +1112,37 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>47783</v>
+        <v>37308</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>328/143</t>
+          <t>580/5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>č. 328/143 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1150,37 +1150,37 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>47782</v>
+        <v>37308</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>414/49</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>č. 414/49 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1188,37 +1188,37 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47781</v>
+        <v>36099</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>414/48</t>
+          <t>160/423</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Stodůlky</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>č. 414/48 Ládví</t>
+          <t>jednotka č. 28180010, garáž v budově č.p. 2818, část obce Stodůlky, na parcele 160/423 Stodůlky, podíl na společných částech domu a pozemku 24784/119926</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1226,37 +1226,37 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>47780</v>
+        <v>35956</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>st. 1294</t>
+          <t>2780/217</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Stodůlky</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stavební č. 1294 Ládví (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>jednotka č. 25480013, garáž v budově č.p. 2548, část obce Stodůlky, na parcele 2780/217 Stodůlky, podíl na společných částech domu a pozemku 2779/628880</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1264,37 +1264,37 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>47779</v>
+        <v>35418</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>95/15</t>
+          <t>2780/217</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Stodůlky</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>č. 95/15 Ládví</t>
+          <t>jednotka č. 25480036, garáž v budově č.p. 2548, část obce Stodůlky, na parcele 2780/217 Stodůlky, podíl na společných částech domu a pozemku 2779/628880</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>47778</v>
+        <v>33434</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>96/5</t>
+          <t>580/5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>č. 96/5 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1340,37 +1340,37 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47777</v>
+        <v>33434</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>97/10</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>č. 97/10 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1378,37 +1378,37 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>47776</v>
+        <v>33430</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>st. 1315</t>
+          <t>580/5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stavební č. 1315 Ládví (součástí je stavba č.p. 2132, čst obce Ládví)</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1416,37 +1416,37 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>47775</v>
+        <v>33430</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>511/4</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>č. 511/4 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1454,37 +1454,37 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>47774</v>
+        <v>33351</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>103/17</t>
+          <t>580/5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>č. 103/17 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1492,37 +1492,37 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>47773</v>
+        <v>33351</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27/10</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>č. 27/10 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1530,37 +1530,37 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>47772</v>
+        <v>33337</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>103/16</t>
+          <t>954</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>č. 103/16 Ládví</t>
+          <t>jednotka č. 16330902, garáž v budově č.p. 1633, část obce Holešovice, na parcele 954 Holešovice (součástí je stavba č.p. 1633, čst obce Holešovice), podíl na společných částech domu a pozemku 28655/130700</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1568,37 +1568,37 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>47771</v>
+        <v>33268</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>103/12</t>
+          <t>580/5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>č. 103/12 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1606,37 +1606,37 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>47770</v>
+        <v>33268</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>102/8</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>č. 102/8 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1644,37 +1644,37 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47769</v>
+        <v>33201</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>103/10</t>
+          <t>580/5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>č. 103/10 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1682,37 +1682,37 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>47768</v>
+        <v>33201</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>103/13</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>č. 103/13 Ládví</t>
+          <t>jednotka č. 16320038, garáž v budově č.p. 1632, část obce Holešovice, na parcele 580/5 Holešovice, 581 Holešovice (součástí je stavba č.p. 1632, čst obce Holešovice), podíl na společných částech domu a pozemku 24385/139693</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1720,13 +1720,13 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>47767</v>
+        <v>32934</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>st. 118</t>
+          <t>734/1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Holešovice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>jednotka č. 11480029, byt v budově č.p. 1148, část obce Ládví, na parcele st. 118 Ládví, podíl na společných částech domu a pozemku 732/32916</t>
+          <t>jednotka č. 8690341, garáž v budově č.p. 869, část obce Holešovice, na parcele 734/1 Holešovice, podíl na společných částech domu a pozemku 2450/197252</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1758,37 +1758,37 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>jednotka na parcele s prefixem st. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>47766</v>
+        <v>31596</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>364/36</t>
+          <t>1061/92</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Liboc</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>č. 364/36 Ládví</t>
+          <t>jednotka č. 6260342, garáž v budově č.p. 626, část obce Liboc, na parcele 1061/92 Liboc, 1061/153 Liboc, 1061/156 Liboc, podíl na společných částech domu a pozemku 201/31365</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1796,37 +1796,37 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>47765</v>
+        <v>31596</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1061/153</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Liboc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>č. 798 Ládví</t>
+          <t>jednotka č. 6260342, garáž v budově č.p. 626, část obce Liboc, na parcele 1061/92 Liboc, 1061/153 Liboc, 1061/156 Liboc, podíl na společných částech domu a pozemku 201/31365</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1834,37 +1834,37 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>47764</v>
+        <v>31596</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>618/9</t>
+          <t>1061/156</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Liboc</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>č. 618/9 Ládví</t>
+          <t>jednotka č. 6260342, garáž v budově č.p. 626, část obce Liboc, na parcele 1061/92 Liboc, 1061/153 Liboc, 1061/156 Liboc, podíl na společných částech domu a pozemku 201/31365</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1872,37 +1872,37 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>47763</v>
+        <v>31344</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>st. 931</t>
+          <t>1818/396</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stavební č. 931 Ládví (součástí je stavba č.p. 1434, čst obce Olešovice)</t>
+          <t>jednotka č. 15860205, garáž v budově č.p. 1586, část obce Hostivař, na parcele 1818/396 Hostivař (součástí je stavba č.p. 1586, čst obce Hostivař), podíl na společných částech domu a pozemku 27680/89507</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1910,37 +1910,37 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>47762</v>
+        <v>30501</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>578/3</t>
+          <t>1818/375</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>č. 578/3 Ládví</t>
+          <t>jednotka č. 15800317, garáž v budově č.p. 1580, část obce Hostivař, na parcele 1818/375 Hostivař, 1818/376 Hostivař, 1818/377 Hostivař (součástí je stavba č.p. 1580, čst obce Hostivař), podíl na společných částech domu a pozemku 28543/155716</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1948,37 +1948,37 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>47761</v>
+        <v>30501</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>578/2</t>
+          <t>1818/376</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>č. 578/2 Ládví</t>
+          <t>jednotka č. 15800317, garáž v budově č.p. 1580, část obce Hostivař, na parcele 1818/375 Hostivař, 1818/376 Hostivař, 1818/377 Hostivař (součástí je stavba č.p. 1580, čst obce Hostivař), podíl na společných částech domu a pozemku 28543/155716</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1986,37 +1986,37 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>47760</v>
+        <v>30501</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>578/1</t>
+          <t>1818/377</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>č. 578/1 Ládví</t>
+          <t>jednotka č. 15800317, garáž v budově č.p. 1580, část obce Hostivař, na parcele 1818/375 Hostivař, 1818/376 Hostivař, 1818/377 Hostivař (součástí je stavba č.p. 1580, čst obce Hostivař), podíl na společných částech domu a pozemku 28543/155716</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2024,37 +2024,37 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47759</v>
+        <v>25660</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>340/1</t>
+          <t>110/1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>č. 340/1 Ládví</t>
+          <t>jednotka č. 5900100, garáž v budově č.p. 590, část obce Štěrboholy, na parcele 110/1 Štěrboholy (součástí je stavba č.p. 590, čst obce Štěrboholy), podíl na společných částech domu a pozemku 27468/80987</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2062,37 +2062,37 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>47758</v>
+        <v>21331</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>432/9</t>
+          <t>527</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Smíchov</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>č. 432/9 Ládví</t>
+          <t>jednotka č. 4940102, garáž v budově č.p. 494, část obce Smíchov, na parcele 527 Smíchov (součástí je stavba č.p. 494, čst obce Smíchov), podíl na společných částech domu a pozemku 283/31473</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2100,37 +2100,37 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>47757</v>
+        <v>19260</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>432/8</t>
+          <t>46/6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Cholupice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>č. 432/8 Ládví</t>
+          <t>jednotka č. 1340101, garáž v budově č.p. 134, část obce Cholupice, na parcele 46/6 Cholupice, podíl na společných částech domu a pozemku 26236/37916</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2138,37 +2138,37 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>47756</v>
+        <v>19136</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>430/2</t>
+          <t>2715/2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Dejvice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>č. 430/2 Ládví</t>
+          <t>jednotka č. 28220301, garáž v budově č.p. 2822, část obce Dejvice, na parcele 2715/2 Dejvice (součástí je stavba č.p. 2822, čst obce Dejvice), 2715/96 Dejvice, 2715/97 Dejvice, podíl na společných částech domu a pozemku 21306/116531</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2176,37 +2176,37 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>47755</v>
+        <v>19136</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>459/9</t>
+          <t>2715/96</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Dejvice</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>č. 459/9 Ládví</t>
+          <t>jednotka č. 28220301, garáž v budově č.p. 2822, část obce Dejvice, na parcele 2715/2 Dejvice (součástí je stavba č.p. 2822, čst obce Dejvice), 2715/96 Dejvice, 2715/97 Dejvice, podíl na společných částech domu a pozemku 21306/116531</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2214,37 +2214,37 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47754</v>
+        <v>19136</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>st. 1186</t>
+          <t>2715/97</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Dejvice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stavební č. 1186 Ládví (součástí je stavba budova bez čp/če, jiná stavba)</t>
+          <t>jednotka č. 28220301, garáž v budově č.p. 2822, část obce Dejvice, na parcele 2715/2 Dejvice (součástí je stavba č.p. 2822, čst obce Dejvice), 2715/96 Dejvice, 2715/97 Dejvice, podíl na společných částech domu a pozemku 21306/116531</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2252,37 +2252,37 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>47753</v>
+        <v>17392</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>st. 476</t>
+          <t>4817/5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stavební č. 476 Ládví (součástí je stavba č.e. 1424, čst obce Ládví)</t>
+          <t>jednotka č. 23900002, garáž v budově č.p. 2390, část obce Modřany, na parcele 4817/5 Modřany, 4825/9 Modřany (součástí je stavba č.p. 2390, čst obce Modřany), podíl na společných částech domu a pozemku 21507/227640</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2290,37 +2290,37 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>47752</v>
+        <v>17392</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>519/1</t>
+          <t>4825/9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>č. 519/1 Ládví</t>
+          <t>jednotka č. 23900002, garáž v budově č.p. 2390, část obce Modřany, na parcele 4817/5 Modřany, 4825/9 Modřany (součástí je stavba č.p. 2390, čst obce Modřany), podíl na společných částech domu a pozemku 21507/227640</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2328,37 +2328,37 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>více parcel oddělených čárkou</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>47751</v>
+        <v>16986</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>jednotka</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Praha-východ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>st. 128</t>
+          <t>2780/217</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ládví</t>
+          <t>Stodůlky</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stavební č. 128 Ládví (součástí je stavba č.e. 1485, čst obce Ládví)</t>
+          <t>jednotka č. 25480162, garáž v budově č.p. 2548, část obce Stodůlky, na parcele 2780/217 Stodůlky, podíl na společných částech domu a pozemku 2779/628880</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2366,7 +2366,767 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>16435</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3448</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>jednotka č. 33810102, garáž v budově č.p. 3381, část obce Smíchov, na parcele 3448 Smíchov (součástí je stavba č.p. 3381, čst obce Smíchov), podíl na společných částech domu a pozemku 2946/19124</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16373</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3448</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>jednotka č. 33810102, garáž v budově č.p. 3381, část obce Smíchov, na parcele 3448 Smíchov (součástí je stavba č.p. 3381, čst obce Smíchov), podíl na společných částech domu a pozemku 2946/19124</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>16331</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3109/20</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>jednotka č. 33540101, garáž v budově č.p. 3354, část obce Smíchov, na parcele 3109/20 Smíchov (součástí je stavba č.p. 3354, čst obce Smíchov), podíl na společných částech domu a pozemku 21600/76084</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>14903</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4817/5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Modřany</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>jednotka č. 23900002, garáž v budově č.p. 2390, část obce Modřany, na parcele 4817/5 Modřany, 4825/9 Modřany (součástí je stavba č.p. 2390, čst obce Modřany), podíl na společných částech domu a pozemku 21507/227640</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>14903</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4825/9</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Modřany</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>jednotka č. 23900002, garáž v budově č.p. 2390, část obce Modřany, na parcele 4817/5 Modřany, 4825/9 Modřany (součástí je stavba č.p. 2390, čst obce Modřany), podíl na společných částech domu a pozemku 21507/227640</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>13623</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3109/20</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>jednotka č. 33540101, garáž v budově č.p. 3354, část obce Smíchov, na parcele 3109/20 Smíchov (součástí je stavba č.p. 3354, čst obce Smíchov), podíl na společných částech domu a pozemku 21600/76084</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>12849</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2780/217</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Stodůlky</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>jednotka č. 25480082, garáž v budově č.p. 2548, část obce Stodůlky, na parcele 2780/217 Stodůlky, podíl na společných částech domu a pozemku 2779/628880</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>12839</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2780/217</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Stodůlky</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>jednotka č. 25480066, garáž v budově č.p. 2548, část obce Stodůlky, na parcele 2780/217 Stodůlky, podíl na společných částech domu a pozemku 2779/628880</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>12708</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1061/91</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Liboc</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>jednotka č. 6270201, garáž v budově č.p. 627, část obce Liboc, na parcele 1061/91 Liboc, podíl na společných částech domu a pozemku 2073/328428</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>11783</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3109/20</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>jednotka č. 33540101, garáž v budově č.p. 3354, část obce Smíchov, na parcele 3109/20 Smíchov (součástí je stavba č.p. 3354, čst obce Smíchov), podíl na společných částech domu a pozemku 21600/76084</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>11710</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3109/20</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>jednotka č. 33540101, garáž v budově č.p. 3354, část obce Smíchov, na parcele 3109/20 Smíchov (součástí je stavba č.p. 3354, čst obce Smíchov), podíl na společných částech domu a pozemku 21600/76084</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>10936</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>jednotka č. 33310101, garáž v budově č.p. 3331, část obce Smíchov, na parcele 3443 Smíchov (součástí je stavba č.p. 3331, čst obce Smíchov), podíl na společných částech domu a pozemku 29648/145749</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>10672</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2183/139</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Žižkov</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>jednotka č. 28220001, garáž v budově č.p. 2822, část obce Žižkov, na parcele 2183/139 Žižkov, podíl na společných částech domu a pozemku 2339/14798</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>8863</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2342/472</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Stodůlky</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>jednotka č. 25660240, garáž v budově č.p. 2566, část obce Stodůlky, na parcele 2342/472 Stodůlky, 2342/473 Stodůlky, podíl na společných částech domu a pozemku 201/28865</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>8863</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2342/473</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Stodůlky</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>jednotka č. 25660240, garáž v budově č.p. 2566, část obce Stodůlky, na parcele 2342/472 Stodůlky, 2342/473 Stodůlky, podíl na společných částech domu a pozemku 201/28865</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>více parcel oddělených čárkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7949</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3109/20</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>jednotka č. 33540101, garáž v budově č.p. 3354, část obce Smíchov, na parcele 3109/20 Smíchov (součástí je stavba č.p. 3354, čst obce Smíchov), podíl na společných částech domu a pozemku 21600/76084</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7380</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>jednotka č. 4940103, garáž v budově č.p. 494, část obce Smíchov, na parcele 527 Smíchov (součástí je stavba č.p. 494, čst obce Smíchov), podíl na společných částech domu a pozemku 283/31473</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7352</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3109/20</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Smíchov</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>jednotka č. 33540101, garáž v budově č.p. 3354, část obce Smíchov, na parcele 3109/20 Smíchov (součástí je stavba č.p. 3354, čst obce Smíchov), podíl na společných částech domu a pozemku 21600/76084</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2557</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2183/139</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Žižkov</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>jednotka č. 28220002, garáž v budově č.p. 2822, část obce Žižkov, na parcele 2183/139 Žižkov, podíl na společných částech domu a pozemku 2212/14798</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>jednotka</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>162/279</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Stodůlky</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>jednotka č. 27290907, garáž v budově č.p. 2729, část obce Stodůlky, na parcele 162/279 Stodůlky, podíl na společných částech domu a pozemku 24657/144950</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>jednotka na parcele bez prefixu st. + KU</t>
         </is>
       </c>
     </row>

--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>37283</v>
+        <v>27854</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2131/26</t>
+          <t>2838/22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jednotka č. 20570023, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 7294/839119</t>
+          <t>č. 2838/22 Strašnice</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -504,17 +504,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>37283</v>
+        <v>68251</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -524,17 +524,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2131/27</t>
+          <t>1200/2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>jednotka č. 20570023, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 7294/839119</t>
+          <t>č. 1200/2 Hostivař</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>37283</v>
+        <v>27875</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -562,17 +562,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2131/28</t>
+          <t>2838/118</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>jednotka č. 20570023, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 7294/839119</t>
+          <t>č. 2838/118 Strašnice</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -580,17 +580,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>37283</v>
+        <v>26224</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2131/29</t>
+          <t>378/114</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jednotka č. 20570023, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 7294/839119</t>
+          <t>č. 378/114 Štěrboholy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -618,17 +618,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>37282</v>
+        <v>68265</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -638,17 +638,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>160/773</t>
+          <t>903/35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>jednotka č. 29470010, jiný nebytový prostor v budově č.p. 2947, část obce Stodůlky, na parcele 160/773 Stodůlky (součástí je stavba č.p. 2947, čst obce Stodůlky), podíl na společných částech domu a pozemku 14243/92994</t>
+          <t>č. 903/35 Malešice</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -656,17 +656,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>37281</v>
+        <v>25179</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -676,17 +676,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>160/773</t>
+          <t>378/75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jednotka č. 29470906, byt v budově č.p. 2947, část obce Stodůlky, na parcele 160/773 Stodůlky (součástí je stavba č.p. 2947, čst obce Stodůlky), podíl na společných částech domu a pozemku 591/92994</t>
+          <t>č. 378/75 Štěrboholy</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -694,13 +694,13 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37280</v>
+        <v>30732</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -714,17 +714,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>370/151</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>č. 2969 Stodůlky</t>
+          <t>č. 370/151 Hostivař</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,7 +738,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>37279</v>
+        <v>30750</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -752,17 +752,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>370/145</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>č. 2967 Stodůlky</t>
+          <t>č. 370/145 Hostivař</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -776,7 +776,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>37278</v>
+        <v>68357</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -790,17 +790,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>415/57</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 2973 Stodůlky</t>
+          <t>č. 415/57 Štěrboholy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -814,7 +814,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>37277</v>
+        <v>27851</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2794/20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>č. 2965 Stodůlky</t>
+          <t>č. 2794/20 Strašnice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -852,7 +852,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>37276</v>
+        <v>24869</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -866,17 +866,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>903/35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>č. 2976 Stodůlky</t>
+          <t>č. 903/35 Malešice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -890,7 +890,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>37275</v>
+        <v>68439</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -904,17 +904,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3432/47</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>č. 2977 Stodůlky</t>
+          <t>č. 3432/47 Strašnice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -928,7 +928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37274</v>
+        <v>68376</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -942,17 +942,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2798/21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>č. 2970 Stodůlky</t>
+          <t>č. 2798/21 Strašnice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -966,7 +966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37273</v>
+        <v>27827</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -980,17 +980,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3118/98</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>č. 2974 Stodůlky</t>
+          <t>č. 3118/98 Strašnice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1004,11 +1004,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37272</v>
+        <v>26215</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>348/155</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>č. 2964 Stodůlky</t>
+          <t>č. 348/155 Štěrboholy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>37271</v>
+        <v>30749</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>1818/253</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>č. 2971 Stodůlky</t>
+          <t>č. 1818/253 Hostivař</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37270</v>
+        <v>68472</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2798/36</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 2798/36 Strašnice</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1112,17 +1112,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>37270</v>
+        <v>26204</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>242/15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 242/15 Štěrboholy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>37270</v>
+        <v>68347</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1170,17 +1170,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>584/318</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Dolní Měcholupy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 584/318 Dolní Měcholupy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>37270</v>
+        <v>27862</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>3118/98</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 3118/98 Strašnice</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>37270</v>
+        <v>68349</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>370/217</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 370/217 Štěrboholy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>37270</v>
+        <v>68261</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>1766/32</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 1766/32 Hostivař</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>37270</v>
+        <v>24844</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>903/35</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 903/35 Malešice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>37270</v>
+        <v>24848</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>806/216</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 806/216 Malešice</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>37270</v>
+        <v>26194</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1398,17 +1398,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>113/1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 113/1 Štěrboholy</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1416,17 +1416,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>37270</v>
+        <v>30812</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>1818/25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 1818/25 Hostivař</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>37270</v>
+        <v>68446</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>jednotka č. 21480208, garáž v budově č.p. 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, část obce Stodůlky, na parcele 2964 Stodůlky, 2965 Stodůlky, 2967 Stodůlky, 2968 Stodůlky, 2969 Stodůlky, 2970 Stodůlky, 2973 Stodůlky, 2974 Stodůlky, 2975 Stodůlky, 2976 Stodůlky, 2977 Stodůlky, podíl na společných částech domu a pozemku 366/476600</t>
+          <t>č. 2344 Strašnice</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>37269</v>
+        <v>68243</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1512,17 +1512,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2131/262</t>
+          <t>2078/464</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Záběhlice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>jednotka č. 19550002, byt v budově č.p. 1955, 1950, 1951, 1952, 1953, 1954, část obce Stodůlky, na parcele 2131/262 Stodůlky (součástí je stavba č.p. 1955, 1950, 1951, 1952, 1953, 1954, čst obce Stodůlky), podíl na společných částech domu a pozemku 4466/1192569</t>
+          <t>č. 2078/464 Záběhlice</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>37268</v>
+        <v>28031</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2337/81</t>
+          <t>317/1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>jednotka č. 14650013, byt v budově č.p. 1465, část obce Stodůlky, na parcele 2337/81 Stodůlky, podíl na společných částech domu a pozemku 589/12411</t>
+          <t>č. 317/1 Strašnice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>37267</v>
+        <v>31096</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1588,17 +1588,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2131/86</t>
+          <t>989/1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>jednotka č. 20440001, byt v budově č.p. 2044, část obce Stodůlky, na parcele 2131/86 Stodůlky, podíl na společných částech domu a pozemku 6748/206878</t>
+          <t>č. 989/1 Hostivař</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1606,13 +1606,13 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>37266</v>
+        <v>26222</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2780/356</t>
+          <t>255/111</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>č. 2780/356 Stodůlky</t>
+          <t>č. 255/111 Štěrboholy</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1650,11 +1650,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>37265</v>
+        <v>26217</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2780/305</t>
+          <t>348/214</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>jednotka č. 25760320, garáž v budově č.p. 2576, část obce Stodůlky, na parcele 2780/305 Stodůlky, 2780/355 Stodůlky, 2780/356 Stodůlky, podíl na společných částech domu a pozemku 61/9402</t>
+          <t>č. 348/214 Štěrboholy</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1682,17 +1682,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>37265</v>
+        <v>28074</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1702,17 +1702,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2780/355</t>
+          <t>317/8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>jednotka č. 25760320, garáž v budově č.p. 2576, část obce Stodůlky, na parcele 2780/305 Stodůlky, 2780/355 Stodůlky, 2780/356 Stodůlky, podíl na společných částech domu a pozemku 61/9402</t>
+          <t>č. 317/8 Strašnice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>37265</v>
+        <v>31116</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2780/356</t>
+          <t>1818/21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>jednotka č. 25760320, garáž v budově č.p. 2576, část obce Stodůlky, na parcele 2780/305 Stodůlky, 2780/355 Stodůlky, 2780/356 Stodůlky, podíl na společných částech domu a pozemku 61/9402</t>
+          <t>č. 1818/21 Hostivař</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1758,17 +1758,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>37264</v>
+        <v>26219</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2131/26</t>
+          <t>326/1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>jednotka č. 20540022, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 9011/839119</t>
+          <t>č. 326/1 Štěrboholy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37264</v>
+        <v>28035</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2131/27</t>
+          <t>2637/7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>jednotka č. 20540022, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 9011/839119</t>
+          <t>č. 2637/7 Strašnice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37264</v>
+        <v>28043</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1854,17 +1854,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2131/28</t>
+          <t>3925/16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>jednotka č. 20540022, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 9011/839119</t>
+          <t>č. 3925/16 Strašnice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>37264</v>
+        <v>68506</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2131/29</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>jednotka č. 20540022, byt v budově č.p. 2057, 2054, 2055, 2056, část obce Stodůlky, na parcele 2131/26 Stodůlky, 2131/27 Stodůlky, 2131/28 Stodůlky, 2131/29 Stodůlky, podíl na společných částech domu a pozemku 9011/839119</t>
+          <t>č. 1222 Hostivař</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1910,17 +1910,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>37263</v>
+        <v>27972</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1930,17 +1930,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2780/165</t>
+          <t>2838/64</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>č. 2780/165 Stodůlky</t>
+          <t>č. 2838/64 Strašnice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>37262</v>
+        <v>27966</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2780/165</t>
+          <t>2244/110</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>jednotka č. 25220003, byt v budově č.p. 2522, část obce Stodůlky, na parcele 2780/165 Stodůlky, podíl na společných částech domu a pozemku 13592/683778</t>
+          <t>č. 2244/110 Strašnice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>37261</v>
+        <v>25249</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2121/2</t>
+          <t>242/17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>jednotka č. 26040001, garáž v budově č.p. 2604, část obce Stodůlky, na parcele 2121/2 Stodůlky, podíl na společných částech domu a pozemku 43980/251890</t>
+          <t>č. 242/17 Štěrboholy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2024,17 +2024,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>37260</v>
+        <v>68493</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2121/2</t>
+          <t>1766/32</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>jednotka č. 26040033, byt v budově č.p. 2604, část obce Stodůlky, na parcele 2121/2 Stodůlky, podíl na společných částech domu a pozemku 12611/251890</t>
+          <t>č. 1766/32 Hostivař</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>37259</v>
+        <v>24841</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2082,17 +2082,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>151/24</t>
+          <t>902/8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>jednotka č. 15500003, byt v budově č.p. 1551, 1547, 1548, 1549, 1550, část obce Stodůlky, na parcele 151/24 Stodůlky, 151/25 Stodůlky, 151/26 Stodůlky, 151/27 Stodůlky, 151/28 Stodůlky, podíl na společných částech domu a pozemku 6967/750632</t>
+          <t>č. 902/8 Malešice</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2100,17 +2100,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>37259</v>
+        <v>68520</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>151/25</t>
+          <t>223/4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>jednotka č. 15500003, byt v budově č.p. 1551, 1547, 1548, 1549, 1550, část obce Stodůlky, na parcele 151/24 Stodůlky, 151/25 Stodůlky, 151/26 Stodůlky, 151/27 Stodůlky, 151/28 Stodůlky, podíl na společných částech domu a pozemku 6967/750632</t>
+          <t>č. 223/4 Malešice</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>37259</v>
+        <v>68984</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>151/26</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>jednotka č. 15500003, byt v budově č.p. 1551, 1547, 1548, 1549, 1550, část obce Stodůlky, na parcele 151/24 Stodůlky, 151/25 Stodůlky, 151/26 Stodůlky, 151/27 Stodůlky, 151/28 Stodůlky, podíl na společných částech domu a pozemku 6967/750632</t>
+          <t>č. 119 Štěrboholy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>37259</v>
+        <v>68537</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>151/27</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>jednotka č. 15500003, byt v budově č.p. 1551, 1547, 1548, 1549, 1550, část obce Stodůlky, na parcele 151/24 Stodůlky, 151/25 Stodůlky, 151/26 Stodůlky, 151/27 Stodůlky, 151/28 Stodůlky, podíl na společných částech domu a pozemku 6967/750632</t>
+          <t>č. 119 Štěrboholy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>37259</v>
+        <v>68992</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>151/28</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>jednotka č. 15500003, byt v budově č.p. 1551, 1547, 1548, 1549, 1550, část obce Stodůlky, na parcele 151/24 Stodůlky, 151/25 Stodůlky, 151/26 Stodůlky, 151/27 Stodůlky, 151/28 Stodůlky, podíl na společných částech domu a pozemku 6967/750632</t>
+          <t>č. 119 Štěrboholy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>37258</v>
+        <v>68525</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2131/180</t>
+          <t>903/35</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>jednotka č. 27220100, byt v budově č.p. 2722, část obce Stodůlky, na parcele 2131/180 Stodůlky, podíl na společných částech domu a pozemku 6087/1627256</t>
+          <t>č. 903/35 Malešice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>37257</v>
+        <v>68500</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2310,17 +2310,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2849/1</t>
+          <t>1818/253</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 1818/253 Hostivař</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2328,17 +2328,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>37257</v>
+        <v>26227</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2849/2</t>
+          <t>349/25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 349/25 Štěrboholy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>37257</v>
+        <v>28057</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2386,17 +2386,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2849/4</t>
+          <t>3925/16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 3925/16 Strašnice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2404,17 +2404,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>37257</v>
+        <v>28007</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2424,17 +2424,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2850/1</t>
+          <t>3233/3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 3233/3 Strašnice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>37257</v>
+        <v>68583</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2850/3</t>
+          <t>2438/1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 2438/1 Strašnice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>37257</v>
+        <v>30888</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2851/1</t>
+          <t>1740/12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 1740/12 Hostivař</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2518,17 +2518,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>37257</v>
+        <v>68528</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2851/2</t>
+          <t>2244/2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 2244/2 Strašnice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>37257</v>
+        <v>68625</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2852/1</t>
+          <t>1831/1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 1831/1 Strašnice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2594,17 +2594,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>37257</v>
+        <v>68610</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2614,17 +2614,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2852/2</t>
+          <t>2798/172</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 2798/172 Strašnice</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2632,17 +2632,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>37257</v>
+        <v>27979</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2852/3</t>
+          <t>2244/24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>jednotka č. 25640013, byt v budově č.p. 2565, 2560, 2561, 2562, 2563, 2564, část obce Stodůlky, na parcele 2849/1 Stodůlky, 2849/2 Stodůlky, 2849/4 Stodůlky, 2850/1 Stodůlky, 2850/3 Stodůlky, 2851/1 Stodůlky, 2851/2 Stodůlky, 2852/1 Stodůlky, 2852/2 Stodůlky, 2852/3 Stodůlky, podíl na společných částech domu a pozemku 4040/1217029</t>
+          <t>č. 2244/24 Strašnice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2670,13 +2670,13 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>více parcel oddělených čárkou</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>37256</v>
+        <v>26184</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1947/5</t>
+          <t>196/39</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>č. 1947/5 Stodůlky</t>
+          <t>č. 196/39 Štěrboholy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2714,7 +2714,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>37255</v>
+        <v>68517</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2728,17 +2728,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1947/1</t>
+          <t>806/205</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>č. 1947/1 Stodůlky</t>
+          <t>č. 806/205 Malešice</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -2752,7 +2752,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>37254</v>
+        <v>28033</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2766,17 +2766,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1947/4</t>
+          <t>2796/116</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>č. 1947/4 Stodůlky</t>
+          <t>č. 2796/116 Strašnice</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>37253</v>
+        <v>30916</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2804,17 +2804,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2010/225</t>
+          <t>1818/28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>č. 2010/225 Stodůlky</t>
+          <t>č. 1818/28 Hostivař</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -2828,7 +2828,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>37252</v>
+        <v>24881</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2842,17 +2842,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2010/224</t>
+          <t>64/10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>č. 2010/224 Stodůlky</t>
+          <t>č. 64/10 Malešice</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -2866,11 +2866,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>37251</v>
+        <v>28017</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1947/8</t>
+          <t>4031/112</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>č. 1947/8 Stodůlky (součástí je stavba č.p. 772, čst obce Stodůlky)</t>
+          <t>č. 4031/112 Strašnice</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2898,17 +2898,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>37250</v>
+        <v>68586</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2131/46</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>jednotka č. 19390003, byt v budově č.p. 1939, část obce Stodůlky, na parcele 2131/46 Stodůlky, podíl na společných částech domu a pozemku 558/53725</t>
+          <t>č. 248 Strašnice</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2936,13 +2936,13 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>37249</v>
+        <v>30606</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2956,17 +2956,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2315/1</t>
+          <t>1766/13</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>č. 2315/1 Stodůlky</t>
+          <t>č. 1766/13 Hostivař</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2980,11 +2980,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>37248</v>
+        <v>24875</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2994,17 +2994,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2315/78</t>
+          <t>1025/1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>jednotka č. 26150035, jiný nebytový prostor v budově č.p. 2615, část obce Stodůlky, na parcele 2315/78 Stodůlky, podíl na společných částech domu a pozemku 18/39105</t>
+          <t>č. 1025/1 Malešice</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>37247</v>
+        <v>30921</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jednotka</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2315/78</t>
+          <t>1818/28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>jednotka č. 26150205, byt v budově č.p. 2615, část obce Stodůlky, na parcele 2315/78 Stodůlky, podíl na společných částech domu a pozemku 404/39105</t>
+          <t>č. 1818/28 Hostivař</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3050,13 +3050,13 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>jednotka na parcele bez prefixu st. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>37246</v>
+        <v>30926</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3070,17 +3070,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>162/839</t>
+          <t>1761/233</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>č. 162/839 Stodůlky</t>
+          <t>č. 1761/233 Hostivař</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3094,7 +3094,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>37245</v>
+        <v>28092</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>162/848</t>
+          <t>4390/105</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>č. 162/848 Stodůlky</t>
+          <t>č. 4390/105 Strašnice</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3132,7 +3132,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>37244</v>
+        <v>24729</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3146,17 +3146,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>162/850</t>
+          <t>2244/2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>č. 162/850 Stodůlky</t>
+          <t>č. 2244/2 Strašnice</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3170,7 +3170,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>37243</v>
+        <v>24888</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3184,17 +3184,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>162/845</t>
+          <t>1025/1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>č. 162/845 Stodůlky</t>
+          <t>č. 1025/1 Malešice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3208,7 +3208,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>37242</v>
+        <v>25287</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3222,17 +3222,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>162/840</t>
+          <t>1025/1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>č. 162/840 Stodůlky</t>
+          <t>č. 1025/1 Malešice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>37241</v>
+        <v>26229</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>162/842</t>
+          <t>349/107</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>č. 162/842 Stodůlky</t>
+          <t>č. 349/107 Štěrboholy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3284,7 +3284,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>37240</v>
+        <v>28077</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3298,17 +3298,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>162/786</t>
+          <t>3925/16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>č. 162/786 Stodůlky</t>
+          <t>č. 3925/16 Strašnice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>37239</v>
+        <v>28089</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>162/849</t>
+          <t>4269/2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>č. 162/849 Stodůlky</t>
+          <t>č. 4269/2 Strašnice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3360,7 +3360,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>37238</v>
+        <v>68480</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3374,17 +3374,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>162/844</t>
+          <t>2742/119</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>č. 162/844 Stodůlky</t>
+          <t>č. 2742/119 Hostivař</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3398,7 +3398,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>37237</v>
+        <v>68572</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3412,17 +3412,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>162/783</t>
+          <t>3220/12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>č. 162/783 Stodůlky</t>
+          <t>č. 3220/12 Strašnice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3436,7 +3436,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>37236</v>
+        <v>28005</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3450,17 +3450,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>162/230</t>
+          <t>4458/2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>č. 162/230 Stodůlky</t>
+          <t>č. 4458/2 Strašnice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3474,7 +3474,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>37235</v>
+        <v>68617</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3488,17 +3488,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>162/846</t>
+          <t>1292/84</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>č. 162/846 Stodůlky</t>
+          <t>č. 1292/84 Strašnice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -3512,7 +3512,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>37234</v>
+        <v>30913</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3526,23 +3526,745 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>162/841</t>
+          <t>654/7</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Stodůlky</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>č. 162/841 Stodůlky</t>
+          <t>č. 654/7 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
         </is>
       </c>
       <c r="G82" t="n">
         <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>68640</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1292/103</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>č. 1292/103 Strašnice</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>28260</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2840/3</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>č. 2840/3 Strašnice</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>68591</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2585/35</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>č. 2585/35 Strašnice</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>68293</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1002/2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Nové Sedlo u Lokte</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>č. 1002/2 Nové Sedlo u Lokte</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>68590</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1292/84</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>č. 1292/84 Strašnice</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>68605</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>č. 2885 Strašnice</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>28286</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4089/1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>č. 4089/1 Strašnice</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>68153</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4031/112</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>č. 4031/112 Strašnice</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>24901</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1025/1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>č. 1025/1 Malešice</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>25275</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1025/1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>č. 1025/1 Malešice</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>25297</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>č. 154 Malešice</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>28199</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2838/64</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>č. 2838/64 Strašnice</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>68633</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2764/37</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>č. 2764/37 Strašnice</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>25280</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1025/1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>č. 1025/1 Malešice</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>68652</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>4307/112</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>č. 4307/112 Strašnice</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>68597</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3237/7</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>č. 3237/7 Strašnice</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>68565</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3115/52</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>č. 3115/52 Strašnice</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>68613</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>č. 2706 Strašnice</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>68477</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1818/25</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>č. 1818/25 Hostivař</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>číslo a KU za ním</t>
         </is>

--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>27854</v>
+        <v>28087</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2838/22</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>č. 2838/22 Strašnice</t>
+          <t>č. 1286 Strašnice (součástí je stavba č.p. 1508, čst obce Strašnice)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -504,13 +504,13 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68251</v>
+        <v>68070</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -524,17 +524,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1200/2</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>č. 1200/2 Hostivař</t>
+          <t>č. 1393 Strašnice</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -548,7 +548,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27875</v>
+        <v>30689</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -562,17 +562,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2838/118</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>č. 2838/118 Strašnice</t>
+          <t>č. 1932 Hostivař</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,7 +586,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>26224</v>
+        <v>24711</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -600,17 +600,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>378/114</t>
+          <t>80/2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>č. 378/114 Štěrboholy</t>
+          <t>č. 80/2 Malešice</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -624,7 +624,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68265</v>
+        <v>68613</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -638,17 +638,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>903/35</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>č. 903/35 Malešice</t>
+          <t>č. 2706 Strašnice</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -662,11 +662,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25179</v>
+        <v>68612</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -676,17 +676,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>378/75</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>č. 378/75 Štěrboholy</t>
+          <t>č. 2705 Strašnice (součástí je stavba č.p. 1203, čst obce Strašnice)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -694,13 +694,13 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30732</v>
+        <v>27496</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -714,17 +714,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>370/151</t>
+          <t>2845/14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>č. 370/151 Hostivař</t>
+          <t>č. 2845/14 Strašnice</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,7 +738,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>30750</v>
+        <v>69178</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>370/145</t>
+          <t>121/4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>č. 370/145 Hostivař</t>
+          <t>č. 121/4 Hostivař</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -776,7 +776,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68357</v>
+        <v>67919</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -790,17 +790,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>415/57</t>
+          <t>3496/9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 415/57 Štěrboholy</t>
+          <t>č. 3496/9 Strašnice</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -814,7 +814,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>27851</v>
+        <v>26489</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2794/20</t>
+          <t>439/37</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>č. 2794/20 Strašnice</t>
+          <t>č. 439/37 Štěrboholy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -852,11 +852,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24869</v>
+        <v>26488</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>903/35</t>
+          <t>439/98</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>č. 903/35 Malešice</t>
+          <t>č. 439/98 Štěrboholy (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -884,17 +884,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68439</v>
+        <v>69243</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3432/47</t>
+          <t>734/2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>č. 3432/47 Strašnice</t>
+          <t>č. 734/2 Malešice (součástí je stavba č.p. 562, čst obce Malešice)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -922,13 +922,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68376</v>
+        <v>69244</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -942,17 +942,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2798/21</t>
+          <t>913/3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>č. 2798/21 Strašnice</t>
+          <t>č. 913/3 Malešice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -966,7 +966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27827</v>
+        <v>69245</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -980,17 +980,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3118/98</t>
+          <t>913/5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>č. 3118/98 Strašnice</t>
+          <t>č. 913/5 Malešice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1004,7 +1004,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>26215</v>
+        <v>69246</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>348/155</t>
+          <t>734/3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>č. 348/155 Štěrboholy</t>
+          <t>č. 734/3 Malešice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1042,7 +1042,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>30749</v>
+        <v>69247</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1818/253</t>
+          <t>735/4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>č. 1818/253 Hostivař</t>
+          <t>č. 735/4 Malešice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1080,7 +1080,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68472</v>
+        <v>69248</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2798/36</t>
+          <t>734/1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>č. 2798/36 Strašnice</t>
+          <t>č. 734/1 Malešice</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1118,7 +1118,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>26204</v>
+        <v>69249</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>242/15</t>
+          <t>913/4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>č. 242/15 Štěrboholy</t>
+          <t>č. 913/4 Malešice</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1156,7 +1156,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68347</v>
+        <v>24921</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>584/318</t>
+          <t>890/68</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dolní Měcholupy</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>č. 584/318 Dolní Měcholupy</t>
+          <t>č. 890/68 Malešice</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1194,7 +1194,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>27862</v>
+        <v>24922</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3118/98</t>
+          <t>943/2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>č. 3118/98 Strašnice</t>
+          <t>č. 943/2 Malešice</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68349</v>
+        <v>24924</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1246,17 +1246,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>370/217</t>
+          <t>908/6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>č. 370/217 Štěrboholy</t>
+          <t>č. 908/6 Malešice</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1270,7 +1270,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>68261</v>
+        <v>24925</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1766/32</t>
+          <t>906/16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>č. 1766/32 Hostivař</t>
+          <t>č. 906/16 Malešice</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1308,7 +1308,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24844</v>
+        <v>68010</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>903/35</t>
+          <t>890/7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>č. 903/35 Malešice</t>
+          <t>č. 890/7 Malešice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24848</v>
+        <v>68011</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>806/216</t>
+          <t>908/8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>č. 806/216 Malešice</t>
+          <t>č. 908/8 Malešice</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1384,7 +1384,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26194</v>
+        <v>68012</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1398,17 +1398,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>113/1</t>
+          <t>906/17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>č. 113/1 Štěrboholy</t>
+          <t>č. 906/17 Malešice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1422,7 +1422,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30812</v>
+        <v>31294</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1818/25</t>
+          <t>386/2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>č. 1818/25 Hostivař</t>
+          <t>č. 386/2 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1460,7 +1460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>68446</v>
+        <v>31295</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>386/1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>č. 2344 Strašnice</t>
+          <t>č. 386/1 Hostivař</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1498,7 +1498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>68243</v>
+        <v>30604</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1512,17 +1512,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2078/464</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Záběhlice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>č. 2078/464 Záběhlice</t>
+          <t>č. 1933 Hostivař</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28031</v>
+        <v>69717</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>317/1</t>
+          <t>1492/21</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>č. 317/1 Strašnice</t>
+          <t>č. 1492/21 Strašnice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1574,7 +1574,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31096</v>
+        <v>30696</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>989/1</t>
+          <t>1676/65</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>č. 989/1 Hostivař</t>
+          <t>č. 1676/65 Hostivař</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1612,7 +1612,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26222</v>
+        <v>30648</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>255/111</t>
+          <t>21/11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>č. 255/111 Štěrboholy</t>
+          <t>č. 21/11 Hostivař</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>26217</v>
+        <v>30649</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>348/214</t>
+          <t>21/12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>č. 348/214 Štěrboholy</t>
+          <t>č. 21/12 Hostivař</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>28074</v>
+        <v>26383</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1702,17 +1702,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>317/8</t>
+          <t>348/76</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>č. 317/8 Strašnice</t>
+          <t>č. 348/76 Štěrboholy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>31116</v>
+        <v>26384</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1740,17 +1740,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1818/21</t>
+          <t>349/293</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>č. 1818/21 Hostivař</t>
+          <t>č. 349/293 Štěrboholy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1764,7 +1764,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>26219</v>
+        <v>26385</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>326/1</t>
+          <t>349/335</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>č. 326/1 Štěrboholy</t>
+          <t>č. 349/335 Štěrboholy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1802,7 +1802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>28035</v>
+        <v>31383</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1816,17 +1816,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2637/7</t>
+          <t>1302/48</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>č. 2637/7 Strašnice</t>
+          <t>č. 1302/48 Hostivař</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>28043</v>
+        <v>30976</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1854,17 +1854,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3925/16</t>
+          <t>654/7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>č. 3925/16 Strašnice</t>
+          <t>č. 654/7 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1878,11 +1878,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>68506</v>
+        <v>68343</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>191/20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>č. 1222 Hostivař</t>
+          <t>budova bez čp/če, jiná stavba, na parcele 191/20 Štěrboholy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1910,17 +1910,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>budova na parcele č.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>27972</v>
+        <v>68352</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1930,17 +1930,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2838/64</t>
+          <t>191/20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>č. 2838/64 Strašnice</t>
+          <t>budova bez čp/če, jiná stavba, na parcele 191/20 Štěrboholy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1948,13 +1948,13 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>budova na parcele č.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27966</v>
+        <v>69306</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2244/110</t>
+          <t>439/2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>č. 2244/110 Strašnice</t>
+          <t>č. 439/2 Štěrboholy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1992,7 +1992,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>25249</v>
+        <v>26116</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>242/17</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>č. 242/17 Štěrboholy</t>
+          <t>č. 269 Štěrboholy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>68493</v>
+        <v>26117</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2044,17 +2044,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1766/32</t>
+          <t>270</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>č. 1766/32 Hostivař</t>
+          <t>č. 270 Štěrboholy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2068,7 +2068,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24841</v>
+        <v>26091</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2082,17 +2082,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>902/8</t>
+          <t>349/227</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>č. 902/8 Malešice</t>
+          <t>č. 349/227 Štěrboholy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2106,7 +2106,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>68520</v>
+        <v>68251</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>223/4</t>
+          <t>1200/2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>č. 223/4 Malešice</t>
+          <t>č. 1200/2 Hostivař</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2144,11 +2144,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>68984</v>
+        <v>68250</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1200/4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>č. 119 Štěrboholy</t>
+          <t>č. 1200/4 Hostivař (součástí je stavba č.p. 1540, čst obce Hostivař)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2176,13 +2176,13 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>68537</v>
+        <v>68341</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>439/52</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>č. 119 Štěrboholy</t>
+          <t>č. 439/52 Štěrboholy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>68992</v>
+        <v>26238</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>439/52</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>č. 119 Štěrboholy</t>
+          <t>č. 439/52 Štěrboholy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2258,7 +2258,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>68525</v>
+        <v>28554</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2272,17 +2272,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>903/35</t>
+          <t>4174/1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>č. 903/35 Malešice</t>
+          <t>č. 4174/1 Strašnice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>68500</v>
+        <v>28555</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2310,17 +2310,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1818/253</t>
+          <t>4174/2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>č. 1818/253 Hostivař</t>
+          <t>č. 4174/2 Strašnice</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2334,7 +2334,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26227</v>
+        <v>28556</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>349/25</t>
+          <t>4174/4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>č. 349/25 Štěrboholy</t>
+          <t>č. 4174/4 Strašnice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2372,7 +2372,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>28057</v>
+        <v>28557</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3925/16</t>
+          <t>4174/5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>č. 3925/16 Strašnice</t>
+          <t>č. 4174/5 Strašnice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2410,7 +2410,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>28007</v>
+        <v>28558</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3233/3</t>
+          <t>4174/3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>č. 3233/3 Strašnice</t>
+          <t>č. 4174/3 Strašnice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2448,7 +2448,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>68583</v>
+        <v>31061</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2438/1</t>
+          <t>1653/3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>č. 2438/1 Strašnice</t>
+          <t>č. 1653/3 Hostivař</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2486,7 +2486,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>30888</v>
+        <v>67745</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2500,17 +2500,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1740/12</t>
+          <t>302/197</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>č. 1740/12 Hostivař</t>
+          <t>č. 302/197 Štěrboholy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>68528</v>
+        <v>30711</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2538,17 +2538,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2244/2</t>
+          <t>654/7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>č. 2244/2 Strašnice</t>
+          <t>č. 654/7 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2562,7 +2562,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>68625</v>
+        <v>68962</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1831/1</t>
+          <t>1653/3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>č. 1831/1 Strašnice</t>
+          <t>č. 1653/3 Hostivař</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2600,7 +2600,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>68610</v>
+        <v>28316</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2798/172</t>
+          <t>4501/152</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>č. 2798/172 Strašnice</t>
+          <t>č. 4501/152 Strašnice</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2638,7 +2638,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>27979</v>
+        <v>30655</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2652,17 +2652,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2244/24</t>
+          <t>2285/1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>č. 2244/24 Strašnice</t>
+          <t>č. 2285/1 Hostivař</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2676,7 +2676,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>26184</v>
+        <v>30656</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>196/39</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>č. 196/39 Štěrboholy</t>
+          <t>č. 2286 Hostivař</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2714,7 +2714,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>68517</v>
+        <v>24814</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>806/205</t>
+          <t>498/4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>č. 806/205 Malešice</t>
+          <t>č. 498/4 Malešice</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -2752,7 +2752,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>28033</v>
+        <v>26227</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2766,17 +2766,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2796/116</t>
+          <t>349/25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>č. 2796/116 Strašnice</t>
+          <t>č. 349/25 Štěrboholy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>30916</v>
+        <v>25179</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2804,17 +2804,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1818/28</t>
+          <t>378/75</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>č. 1818/28 Hostivař</t>
+          <t>č. 378/75 Štěrboholy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -2828,7 +2828,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>24881</v>
+        <v>27408</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2842,17 +2842,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>64/10</t>
+          <t>4241/31</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>č. 64/10 Malešice</t>
+          <t>č. 4241/31 Strašnice</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -2866,7 +2866,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>28017</v>
+        <v>27409</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4031/112</t>
+          <t>4241/9</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>č. 4031/112 Strašnice</t>
+          <t>č. 4241/9 Strašnice</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2904,7 +2904,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>68586</v>
+        <v>27410</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>4241/36</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>č. 248 Strašnice</t>
+          <t>č. 4241/36 Strašnice</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2942,7 +2942,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>30606</v>
+        <v>27411</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2956,17 +2956,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1766/13</t>
+          <t>4241/29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>č. 1766/13 Hostivař</t>
+          <t>č. 4241/29 Strašnice</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2980,7 +2980,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>24875</v>
+        <v>27412</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2994,17 +2994,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1025/1</t>
+          <t>4241/28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>č. 1025/1 Malešice</t>
+          <t>č. 4241/28 Strašnice</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3018,7 +3018,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>30921</v>
+        <v>27399</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3032,17 +3032,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1818/28</t>
+          <t>4241/7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>č. 1818/28 Hostivař</t>
+          <t>č. 4241/7 Strašnice</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>30926</v>
+        <v>27401</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3070,17 +3070,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1761/233</t>
+          <t>4241/30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>č. 1761/233 Hostivař</t>
+          <t>č. 4241/30 Strašnice</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3094,7 +3094,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>28092</v>
+        <v>27402</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4390/105</t>
+          <t>4241/31</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>č. 4390/105 Strašnice</t>
+          <t>č. 4241/31 Strašnice</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3132,7 +3132,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>24729</v>
+        <v>27403</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2244/2</t>
+          <t>4241/1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>č. 2244/2 Strašnice</t>
+          <t>č. 4241/1 Strašnice</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3170,7 +3170,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>24888</v>
+        <v>27404</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3184,17 +3184,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1025/1</t>
+          <t>4241/28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>č. 1025/1 Malešice</t>
+          <t>č. 4241/28 Strašnice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3208,7 +3208,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>25287</v>
+        <v>27405</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3222,17 +3222,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1025/1</t>
+          <t>4241/35</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>č. 1025/1 Malešice</t>
+          <t>č. 4241/35 Strašnice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>26229</v>
+        <v>68584</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>349/107</t>
+          <t>4471/20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>č. 349/107 Štěrboholy</t>
+          <t>č. 4471/20 Strašnice</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3284,7 +3284,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>28077</v>
+        <v>68081</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3925/16</t>
+          <t>4471/21</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>č. 3925/16 Strašnice</t>
+          <t>č. 4471/21 Strašnice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>28089</v>
+        <v>28584</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4269/2</t>
+          <t>4082/26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>č. 4269/2 Strašnice</t>
+          <t>č. 4082/26 Strašnice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3360,7 +3360,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>68480</v>
+        <v>68036</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3374,17 +3374,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2742/119</t>
+          <t>793/112</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>č. 2742/119 Hostivař</t>
+          <t>č. 793/112 Malešice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3398,7 +3398,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>68572</v>
+        <v>30958</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3412,17 +3412,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3220/12</t>
+          <t>1619/4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>č. 3220/12 Strašnice</t>
+          <t>č. 1619/4 Hostivař</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3436,7 +3436,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>28005</v>
+        <v>68591</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4458/2</t>
+          <t>2585/35</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>č. 4458/2 Strašnice</t>
+          <t>č. 2585/35 Strašnice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3474,7 +3474,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>68617</v>
+        <v>25189</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3488,17 +3488,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1292/84</t>
+          <t>378/76</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>č. 1292/84 Strašnice</t>
+          <t>č. 378/76 Štěrboholy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -3512,7 +3512,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>30913</v>
+        <v>31241</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>654/7</t>
+          <t>504/13</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>č. 654/7 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 504/13 Hostivař</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -3550,7 +3550,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>68640</v>
+        <v>69498</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1292/103</t>
+          <t>4302/220</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>č. 1292/103 Strašnice</t>
+          <t>č. 4302/220 Strašnice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -3588,7 +3588,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>28260</v>
+        <v>69499</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2840/3</t>
+          <t>4302/221</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>č. 2840/3 Strašnice</t>
+          <t>č. 4302/221 Strašnice</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3626,11 +3626,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>68591</v>
+        <v>69497</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2585/35</t>
+          <t>4302/66</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>č. 2585/35 Strašnice</t>
+          <t>č. 4302/66 Strašnice (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3658,17 +3658,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>68293</v>
+        <v>69496</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3678,17 +3678,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1002/2</t>
+          <t>4302/65</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nové Sedlo u Lokte</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>č. 1002/2 Nové Sedlo u Lokte</t>
+          <t>č. 4302/65 Strašnice (součástí je stavba budova bez čp/če, jiná stavba)</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3696,13 +3696,13 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>68590</v>
+        <v>31187</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3716,17 +3716,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1292/84</t>
+          <t>2404/7</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>č. 1292/84 Strašnice</t>
+          <t>č. 2404/7 Hostivař</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -3740,11 +3740,11 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>68605</v>
+        <v>69513</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>parcela</t>
+          <t>budova</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3754,17 +3754,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>1721/6</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>č. 2885 Strašnice</t>
+          <t>č. 1721/6 Hostivař (součástí je stavba č.e. 106, čst obce Hostivař)</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -3772,13 +3772,13 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>číslo a KU za ním</t>
+          <t>č. + KU</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>28286</v>
+        <v>69442</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4089/1</t>
+          <t>4241/28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>č. 4089/1 Strašnice</t>
+          <t>č. 4241/28 Strašnice</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -3816,7 +3816,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>68153</v>
+        <v>69443</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>4031/112</t>
+          <t>4241/31</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>č. 4031/112 Strašnice</t>
+          <t>č. 4241/31 Strašnice</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -3854,7 +3854,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>24901</v>
+        <v>69444</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3868,17 +3868,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1025/1</t>
+          <t>4241/35</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>č. 1025/1 Malešice</t>
+          <t>č. 4241/35 Strašnice</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -3892,7 +3892,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>25275</v>
+        <v>69031</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3906,17 +3906,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1025/1</t>
+          <t>3395/16</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>č. 1025/1 Malešice</t>
+          <t>č. 3395/16 Strašnice (součástí je stavba č.p. 2397, čst obce Strašnice)</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>25297</v>
+        <v>69032</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3944,17 +3944,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>3395/18</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>č. 154 Malešice</t>
+          <t>č. 3395/18 Strašnice</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -3968,7 +3968,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>28199</v>
+        <v>68904</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2838/64</t>
+          <t>4323/13</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>č. 2838/64 Strašnice</t>
+          <t>č. 4323/13 Strašnice</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -4006,7 +4006,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>68633</v>
+        <v>69166</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4020,17 +4020,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2764/37</t>
+          <t>2552/3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>č. 2764/37 Strašnice</t>
+          <t>č. 2552/3 Hostivař</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -4044,7 +4044,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>25280</v>
+        <v>26704</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4058,17 +4058,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1025/1</t>
+          <t>1292/84</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>č. 1025/1 Malešice</t>
+          <t>č. 1292/84 Strašnice</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -4082,7 +4082,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>68652</v>
+        <v>69152</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4096,17 +4096,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4307/112</t>
+          <t>2552/4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>č. 4307/112 Strašnice</t>
+          <t>č. 2552/4 Hostivař</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -4120,7 +4120,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>68597</v>
+        <v>26493</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4134,17 +4134,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3237/7</t>
+          <t>439/238</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>č. 3237/7 Strašnice</t>
+          <t>č. 439/238 Štěrboholy</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -4158,7 +4158,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>68565</v>
+        <v>27210</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -4172,17 +4172,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3115/52</t>
+          <t>517/1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Michle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>č. 3115/52 Strašnice</t>
+          <t>č. 517/1 Michle</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -4196,7 +4196,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>68613</v>
+        <v>27212</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>3262/1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Michle</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>č. 2706 Strašnice</t>
+          <t>č. 3262/1 Michle</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -4234,7 +4234,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>68477</v>
+        <v>27213</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4248,23 +4248,3443 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1818/25</t>
+          <t>4045/15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>č. 4045/15 Strašnice</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>27214</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>516/1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Michle</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>č. 516/1 Michle</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>26224</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>378/114</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>č. 378/114 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>26225</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>378/92</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>č. 378/92 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>67888</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4241/29</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>č. 4241/29 Strašnice</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>67889</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>4241/28</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>č. 4241/28 Strašnice</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>67890</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>4241/31</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>č. 4241/31 Strašnice</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>26144</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>196/88</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>č. 196/88 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>26084</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>487/9</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>č. 487/9 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>26487</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>č. 1/2 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>67749</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>378/74</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>č. 378/74 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>69640</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1547/7</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>č. 1547/7 Strašnice</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>26372</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>370/1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>č. 370/1 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>26373</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>370/21</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>č. 370/21 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>26374</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>370/15</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>č. 370/15 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>25913</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>719/7</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>č. 719/7 Malešice</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>25914</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>719/6</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>č. 719/6 Malešice</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>25921</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>686/12</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>č. 686/12 Malešice</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>25922</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>685/9</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>č. 685/9 Malešice</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>25920</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>686/29</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>č. 686/29 Malešice (součástí je stavba budova bez čp/če, jiná stavba)</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>25919</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>686/30</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>č. 686/30 Malešice (součástí je stavba budova bez čp/če, jiná stavba)</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>67979</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2634/8</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>Hostivař</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>č. 1818/25 Hostivař</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>č. 2634/8 Hostivař</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>68701</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2450/10</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>č. 2450/10 Hostivař</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>31175</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1676/123</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>č. 1676/123 Hostivař</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>26348</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>č. 1/2 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>25067</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>749/3</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>č. 749/3 Malešice</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>25249</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>242/17</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>č. 242/17 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>68912</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3432/53</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>č. 3432/53 Strašnice</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>28033</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2796/116</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>č. 2796/116 Strašnice</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>26130</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>239/1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>č. 239/1 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>24647</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>872/27</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>č. 872/27 Malešice</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>25979</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>253/2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>č. 253/2 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>26598</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>803/82</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>č. 803/82 Malešice</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>69290</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>747/9</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>č. 747/9 Malešice</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>25283</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>760/14</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>č. 760/14 Malešice</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>25285</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>757/25</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>č. 757/25 Malešice</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>69482</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>4501/47</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>č. 4501/47 Strašnice</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>27192</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1132/5</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>č. 1132/5 Strašnice</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>27193</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1132/3</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>č. 1132/3 Strašnice</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>30913</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>654/7</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>č. 654/7 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>69179</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1740/24</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>č. 1740/24 Hostivař</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>67754</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>663/117</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>č. 663/117 Malešice</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>67755</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>663/118</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>č. 663/118 Malešice</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>25631</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>378/67</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>č. 378/67 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25632</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>719/1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>č. 719/1 Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>25634</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>378/68</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>č. 378/68 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>28747</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2798/405</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>č. 2798/405 Strašnice</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>31151</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2574/26</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>č. 2574/26 Hostivař</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>31152</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2574/25</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>č. 2574/25 Hostivař</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>68995</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>č. 391 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>24696</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>č. 950 Malešice</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>28005</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>4458/2</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>č. 4458/2 Strašnice</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>24718</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>723/49</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>č. 723/49 Malešice</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>68241</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>370/292</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>č. 370/292 Hostivař</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>27490</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3165/2</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>č. 3165/2 Strašnice</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>27491</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>3173/6</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>č. 3173/6 Strašnice</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>27288</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>budova</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>4031/44</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>č. 4031/44 Strašnice (součástí je stavba budova bez čp/če, jiná stavba)</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>č. + KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>31342</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1767/18</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>č. 1767/18 Hostivař</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>31343</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>1767/47</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>č. 1767/47 Hostivař</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>24725</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>723/191</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>č. 723/191 Malešice</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>26128</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>383/47</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>č. 383/47 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>26469</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>383/29</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>č. 383/29 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>26521</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>874/1</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>č. 874/1 Malešice</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>30710</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2314/28</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>č. 2314/28 Hostivař</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>68720</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>736/2</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>č. 736/2 Malešice</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>25974</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>370/15</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>č. 370/15 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>26180</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>370/36</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>č. 370/36 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>26181</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>370/261</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>č. 370/261 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>26490</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>382/2</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>č. 382/2 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>26492</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>382/1</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>č. 382/1 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>68131</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>4068/19</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>č. 4068/19 Strašnice</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>24888</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>1025/1</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>č. 1025/1 Malešice</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>24889</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>1025/2</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>č. 1025/2 Malešice</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>24890</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>č. 1141 Malešice</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>26872</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>1342/2</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>č. 1342/2 Strašnice</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>31067</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2771/18</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>č. 2771/18 Hostivař</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>31103</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2771/18</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>č. 2771/18 Hostivař</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>31104</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2771/18</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Hostivař</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>č. 2771/18 Hostivař</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>26106</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>586/2</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>č. 586/2 Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>26107</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>586/38</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>č. 586/38 Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>26108</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>302/96</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>č. 302/96 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>26109</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>586/55</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>č. 586/55 Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>26110</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>586/37</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>č. 586/37 Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>26111</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>302/103</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>č. 302/103 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>26112</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>586/58</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>č. 586/58 Dolní Měcholupy</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>26258</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>191/44</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>č. 191/44 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>28738</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>1292/147</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>č. 1292/147 Strašnice</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>28739</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>1292/149</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>č. 1292/149 Strašnice</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>28740</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>1292/151</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Strašnice</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>č. 1292/151 Strašnice</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>26140</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>378/123</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Štěrboholy</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>č. 378/123 Štěrboholy</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>25188</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>737/7</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Malešice</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>č. 737/7 Malešice</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" t="inlineStr">
         <is>
           <t>číslo a KU za ním</t>
         </is>

--- a/GIS2/vystup.xlsx
+++ b/GIS2/vystup.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68070</v>
+        <v>70097</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -481,22 +481,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Dubí u Teplic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>č. 1393 Strašnice</t>
+          <t>č. 171 Dubí u Teplic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14038</v>
+        <v>70126</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -519,22 +519,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1215/4</t>
+          <t>274/92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Záběhlice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>č. 1215/4 Záběhlice (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 274/92 Drahůnky</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -548,7 +548,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14039</v>
+        <v>70138</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -557,22 +557,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1215/1</t>
+          <t>458/20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Záběhlice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>č. 1215/1 Záběhlice</t>
+          <t>č. 458/20 Mstišov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,7 +586,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30689</v>
+        <v>70033</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -595,22 +595,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>367/3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>č. 1932 Hostivař</t>
+          <t>č. 367/3 Běhánky</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -624,7 +624,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24711</v>
+        <v>70032</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -633,22 +633,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>80/2</t>
+          <t>365/10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>č. 80/2 Malešice</t>
+          <t>č. 365/10 Běhánky</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -662,7 +662,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>27496</v>
+        <v>70034</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -671,22 +671,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2845/14</t>
+          <t>274/73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>č. 2845/14 Strašnice</t>
+          <t>č. 274/73 Drahůnky</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -700,7 +700,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69178</v>
+        <v>70110</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -709,22 +709,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>121/4</t>
+          <t>458/21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>č. 121/4 Hostivař</t>
+          <t>č. 458/21 Mstišov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,7 +738,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60368</v>
+        <v>70111</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -747,22 +747,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2587/10</t>
+          <t>458/46</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Záběhlice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>č. 2587/10 Záběhlice</t>
+          <t>č. 458/46 Mstišov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -776,7 +776,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67919</v>
+        <v>70163</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -785,22 +785,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3496/9</t>
+          <t>280/49</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>č. 3496/9 Strašnice</t>
+          <t>č. 280/49 Drahůnky</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -814,7 +814,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>69244</v>
+        <v>70078</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -823,22 +823,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>913/3</t>
+          <t>437/23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>č. 913/3 Malešice</t>
+          <t>č. 437/23 Mstišov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -852,7 +852,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>69245</v>
+        <v>70083</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -861,22 +861,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>913/5</t>
+          <t>437/14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>č. 913/5 Malešice</t>
+          <t>č. 437/14 Mstišov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -890,7 +890,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69246</v>
+        <v>70094</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -899,22 +899,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>734/3</t>
+          <t>274/118</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>č. 734/3 Malešice</t>
+          <t>č. 274/118 Drahůnky</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -928,7 +928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69247</v>
+        <v>70070</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>735/4</t>
+          <t>458/22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>č. 735/4 Malešice</t>
+          <t>č. 458/22 Mstišov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -966,7 +966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>69248</v>
+        <v>70075</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -975,22 +975,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>734/1</t>
+          <t>437/12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>č. 734/1 Malešice</t>
+          <t>č. 437/12 Mstišov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1004,7 +1004,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>69249</v>
+        <v>70076</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1013,22 +1013,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>913/4</t>
+          <t>437/11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>č. 913/4 Malešice</t>
+          <t>č. 437/11 Mstišov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1042,31 +1042,31 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>69243</v>
+        <v>70077</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>budova</t>
+          <t>parcela</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>734/2</t>
+          <t>437/13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>č. 734/2 Malešice (součástí je stavba č.p. 562, čst obce Malešice)</t>
+          <t>č. 437/13 Mstišov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1074,13 +1074,13 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>č. + KU</t>
+          <t>číslo a KU za ním</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24921</v>
+        <v>70128</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1089,22 +1089,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>890/68</t>
+          <t>125/2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Dubí-Pozorka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>č. 890/68 Malešice</t>
+          <t>č. 125/2 Dubí-Pozorka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1118,7 +1118,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24922</v>
+        <v>70129</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1127,22 +1127,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>943/2</t>
+          <t>125/1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Dubí-Pozorka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>č. 943/2 Malešice</t>
+          <t>č. 125/1 Dubí-Pozorka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1156,7 +1156,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24924</v>
+        <v>70086</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>908/6</t>
+          <t>274/135</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>č. 908/6 Malešice</t>
+          <t>č. 274/135 Drahůnky</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1194,7 +1194,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24925</v>
+        <v>70085</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>906/16</t>
+          <t>274/114</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>č. 906/16 Malešice</t>
+          <t>č. 274/114 Drahůnky</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68010</v>
+        <v>70079</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1241,22 +1241,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>890/7</t>
+          <t>437/17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>č. 890/7 Malešice</t>
+          <t>č. 437/17 Mstišov</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1270,7 +1270,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>68011</v>
+        <v>70080</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1279,22 +1279,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>908/8</t>
+          <t>437/16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>č. 908/8 Malešice</t>
+          <t>č. 437/16 Mstišov</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1308,7 +1308,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>68012</v>
+        <v>70081</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1317,22 +1317,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>906/17</t>
+          <t>437/32</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>č. 906/17 Malešice</t>
+          <t>č. 437/32 Mstišov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>31294</v>
+        <v>70082</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1355,22 +1355,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>386/2</t>
+          <t>447/62</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>č. 386/2 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 447/62 Mstišov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1384,7 +1384,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31295</v>
+        <v>70071</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>386/1</t>
+          <t>437/21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>č. 386/1 Hostivař</t>
+          <t>č. 437/21 Mstišov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1422,7 +1422,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30604</v>
+        <v>70072</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1431,22 +1431,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>437/20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>č. 1933 Hostivař</t>
+          <t>č. 437/20 Mstišov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1460,7 +1460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>69717</v>
+        <v>70073</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1492/21</t>
+          <t>447/64</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>č. 1492/21 Strašnice</t>
+          <t>č. 447/64 Mstišov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1498,7 +1498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30696</v>
+        <v>70074</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1507,22 +1507,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1676/65</t>
+          <t>437/31</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>č. 1676/65 Hostivař</t>
+          <t>č. 437/31 Mstišov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30648</v>
+        <v>70035</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1545,22 +1545,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21/11</t>
+          <t>280/34</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>č. 21/11 Hostivař</t>
+          <t>č. 280/34 Drahůnky</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1574,7 +1574,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30649</v>
+        <v>70036</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1583,22 +1583,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21/12</t>
+          <t>280/33</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>č. 21/12 Hostivař</t>
+          <t>č. 280/33 Drahůnky</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1612,7 +1612,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26383</v>
+        <v>70037</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1621,22 +1621,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>348/76</t>
+          <t>274/111</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>č. 348/76 Štěrboholy</t>
+          <t>č. 274/111 Drahůnky</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>26384</v>
+        <v>70038</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1659,22 +1659,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>349/293</t>
+          <t>274/72</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>č. 349/293 Štěrboholy</t>
+          <t>č. 274/72 Drahůnky</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>26385</v>
+        <v>70040</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1697,22 +1697,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>349/335</t>
+          <t>274/109</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>č. 349/335 Štěrboholy</t>
+          <t>č. 274/109 Drahůnky</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>31383</v>
+        <v>70051</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1302/48</t>
+          <t>274/115</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>č. 1302/48 Hostivař</t>
+          <t>č. 274/115 Drahůnky</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1764,7 +1764,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>30976</v>
+        <v>70029</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1773,22 +1773,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>654/7</t>
+          <t>274/117</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>č. 654/7 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 274/117 Drahůnky</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1802,7 +1802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69306</v>
+        <v>70087</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1811,22 +1811,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>439/2</t>
+          <t>280/32</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>č. 439/2 Štěrboholy</t>
+          <t>č. 280/32 Drahůnky</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13967</v>
+        <v>70088</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1849,22 +1849,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>281/9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Záběhlice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>č. 707 Záběhlice</t>
+          <t>č. 281/9 Drahůnky</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1878,7 +1878,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>26116</v>
+        <v>70093</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1887,22 +1887,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>280/35</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>č. 269 Štěrboholy</t>
+          <t>č. 280/35 Drahůnky</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>26117</v>
+        <v>70041</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1925,22 +1925,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>367/9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>č. 270 Štěrboholy</t>
+          <t>č. 367/9 Běhánky</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>26091</v>
+        <v>70039</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1963,22 +1963,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>349/227</t>
+          <t>365/40</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>č. 349/227 Štěrboholy</t>
+          <t>č. 365/40 Běhánky</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1992,7 +1992,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>26238</v>
+        <v>70030</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2001,22 +2001,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>439/52</t>
+          <t>274/116</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>č. 439/52 Štěrboholy</t>
+          <t>č. 274/116 Drahůnky</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>68341</v>
+        <v>70031</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2039,22 +2039,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>439/52</t>
+          <t>274/93</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>č. 439/52 Štěrboholy</t>
+          <t>č. 274/93 Drahůnky</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2068,7 +2068,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>28554</v>
+        <v>70061</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2077,22 +2077,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4174/1</t>
+          <t>274/120</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>č. 4174/1 Strašnice</t>
+          <t>č. 274/120 Drahůnky</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2106,7 +2106,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>28555</v>
+        <v>70062</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2115,22 +2115,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4174/2</t>
+          <t>274/119</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>č. 4174/2 Strašnice</t>
+          <t>č. 274/119 Drahůnky</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>28556</v>
+        <v>70063</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2153,22 +2153,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4174/4</t>
+          <t>281/7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>č. 4174/4 Strašnice</t>
+          <t>č. 281/7 Drahůnky</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>28557</v>
+        <v>70068</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4174/5</t>
+          <t>309/32</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Dubí-Pozorka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>č. 4174/5 Strašnice</t>
+          <t>č. 309/32 Dubí-Pozorka</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>28558</v>
+        <v>70050</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2229,22 +2229,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4174/3</t>
+          <t>268/4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>č. 4174/3 Strašnice</t>
+          <t>č. 268/4 Drahůnky</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2258,7 +2258,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>31061</v>
+        <v>70054</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2267,22 +2267,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1653/3</t>
+          <t>274/75</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>č. 1653/3 Hostivař</t>
+          <t>č. 274/75 Drahůnky</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>67745</v>
+        <v>70058</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>302/197</t>
+          <t>365/29</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>č. 302/197 Štěrboholy</t>
+          <t>č. 365/29 Běhánky</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2334,7 +2334,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30711</v>
+        <v>70059</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>654/7</t>
+          <t>365/24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>č. 654/7 Hostivař (součástí je stavba budova bez čp/če, garáž)</t>
+          <t>č. 365/24 Běhánky</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2372,7 +2372,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>68962</v>
+        <v>70060</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2381,22 +2381,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1653/3</t>
+          <t>274/75</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>č. 1653/3 Hostivař</t>
+          <t>č. 274/75 Drahůnky</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2410,7 +2410,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>28316</v>
+        <v>70052</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2419,22 +2419,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4501/152</t>
+          <t>365/29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>č. 4501/152 Strašnice</t>
+          <t>č. 365/29 Běhánky</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2448,7 +2448,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>64450</v>
+        <v>70053</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2457,22 +2457,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2526/2</t>
+          <t>365/24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Záběhlice</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>č. 2526/2 Záběhlice</t>
+          <t>č. 365/24 Běhánky</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2486,7 +2486,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>30655</v>
+        <v>70159</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2495,22 +2495,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2285/1</t>
+          <t>385</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>č. 2285/1 Hostivař</t>
+          <t>č. 385 Běhánky</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>30656</v>
+        <v>70160</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2533,22 +2533,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>413</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>č. 2286 Hostivař</t>
+          <t>č. 413 Běhánky</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2562,7 +2562,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>24814</v>
+        <v>70161</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2571,22 +2571,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>498/4</t>
+          <t>386</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>č. 498/4 Malešice</t>
+          <t>č. 386 Běhánky</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2600,7 +2600,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>26227</v>
+        <v>70084</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2609,28 +2609,902 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>349/25</t>
+          <t>288/2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>č. 349/25 Štěrboholy</t>
+          <t>č. 288/2 Běhánky</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>70089</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>611/2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Běhánky</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>č. 611/2 Běhánky</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>70090</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Běhánky</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>č. 612 Běhánky</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>70044</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1025/9</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>č. 1025/9 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>70109</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>278/1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>č. 278/1 Drahůnky</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>70101</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>283/1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>č. 283/1 Drahůnky</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>70102</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>365/32</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Běhánky</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>č. 365/32 Běhánky</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>70099</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>365/31</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Běhánky</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>č. 365/31 Běhánky</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>70100</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>365/34</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Běhánky</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>č. 365/34 Běhánky</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>70115</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>č. 1307 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>70116</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>č. 1339 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>70117</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>č. 1345 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70118</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>č. 1340 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70119</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>č. 1343 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70120</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>č. 1346 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>70121</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>č. 1365 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>70122</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>č. 1371 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>70123</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1341/1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>č. 1341/1 Dubí u Teplic</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>70095</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>252/2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>č. 252/2 Drahůnky</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>70091</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>255/2</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>č. 255/2 Drahůnky</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>70092</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>256/2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>č. 256/2 Drahůnky</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>70151</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Dubí-Pozorka</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>č. 529 Dubí-Pozorka</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>70146</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>525/1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Dubí-Pozorka</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>č. 525/1 Dubí-Pozorka</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>číslo a KU za ním</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>70147</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>525/26</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Dubí-Pozorka</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>č. 525/26 Dubí-Pozorka</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>číslo a KU za ním</t>
         </is>
